--- a/Översikt OSBY.xlsx
+++ b/Översikt OSBY.xlsx
@@ -601,7 +601,7 @@
         <v>45589</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>46134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45177</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45844</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>44802</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>44827</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>46241</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>45796</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>46030</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>46134</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>46134</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>46153</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>44472</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>46153</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45078</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45918</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>45607</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>45356</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>45867</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>44622</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>44813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44461</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>44722</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>44788</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45117</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>45177</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>45033</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>45217</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>45799</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>45905</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45909</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>45925</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44788</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>45999</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>46170</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>45002</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>45364</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>46178</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>46183</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>46189</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>45126</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>44698</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>45255</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>44910</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>45649</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>46275</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>44902</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>45272</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>45182</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45446</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>45735</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>44586</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>44459</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44553</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44579</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>44523</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44472</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>44693</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>44461</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>44845</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>44869</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>44830</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>44603</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>44827</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>44523</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>44687</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>44522</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>44650</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>44813</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>44694</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44746</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>44482</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>44481</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>44572</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>44529</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>44813</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44813</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>44764</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>44762</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>44510</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>44510</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>44478</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>44575</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>44462</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>44468</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>44595</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>44516</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>44487</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>44505</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>44459</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>44459</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>44806</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>44731</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>44610</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>44557</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>44843</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>44609</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>44700</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>44469</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>44662</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>44830</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>44830</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>44831</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v>44475</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>44823</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>44553</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>44614</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>44788</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>44805</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>44623</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>44788</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>44721</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>44834</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>44610</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>44469</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>44573</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>44573</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>45447</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>45369</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>45607</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>44965</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>44881</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44900</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>45078</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>45063</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>45196</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>44895</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>45453</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>44994</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>45259</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>45709</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
         <v>45035</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         <v>45037</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>45666</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>45238</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>45015</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>45268</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>44740</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>45019</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>45643</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>45652</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>45097</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>45573</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45231</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>45231</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>45605</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>45605</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>45353</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>44790</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>45728</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>44904</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>44904</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>45211</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>45506</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>44585</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>44594</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>45646</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>45733</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>45555</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>45631</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44904</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>45209</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>45362</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>44662</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>45722</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>44921</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>44585</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>45568</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>45548</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45683</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>44903</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>45685</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>44832</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>44481</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>45609</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>45110</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>45062</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>44585</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>44826</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>45471</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45537</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>44602</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>44742</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>45243</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>45082</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>44580</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>45093</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>45036</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44801</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>45730</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45240</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44916</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>45463</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>45015</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45468</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>45483</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>44749</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>45404</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>44867</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>44663</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45656</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>45273</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>45666</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>44743</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45033</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45037</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45107</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>44529</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>44746</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>44832</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>44783</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45524</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45162</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>45762</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>44511</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>44978</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>45154</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>44757</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>45323</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>45539</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>44951</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45369</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>45884</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>45785</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45175</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>45642</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44620</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>45390</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>45100</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>45141</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>44644</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>45342</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>45436</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         <v>45695</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>45632</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>45534</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>45534</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>45141</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>45666</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>44845</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>45884</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>45677</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20782,7 +20782,7 @@
         <v>45902</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>44711</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>44524</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>44524</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>45936</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45905</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>45908</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45909</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>45911</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45911</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>45911</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>45911</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>46140</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>45575</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45912</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>44477</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44776</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>45282</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22101,7 +22101,7 @@
         <v>45923</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>44790</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22247,7 +22247,7 @@
         <v>45589</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22320,7 +22320,7 @@
         <v>45589</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22393,7 +22393,7 @@
         <v>44463</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>45686</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>44904</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45930</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>45011</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>45414</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>45506</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>45091</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>44902</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>45434</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>45648</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>45119</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>45961</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>45937</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>44838</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23493,7 +23493,7 @@
         <v>45937</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>45937</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>45937</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45589</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45197</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45610</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45737</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>46153</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>45012</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>46150</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>46153</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>44658</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>46153</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24482,7 +24482,7 @@
         <v>45369</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>46153</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         <v>45733</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>46153</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>45964</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>45964</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>46155</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45237</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>46153</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>45360</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>45148</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>45973</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>45971</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25451,7 +25451,7 @@
         <v>44557</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>45404</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>45154</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>44911</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>45975</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25816,7 +25816,7 @@
         <v>45208</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>45436</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>45706</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>45982</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>45915</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>45630</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>46155</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>46079</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26400,7 +26400,7 @@
         <v>45986</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>44610</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>45443</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26619,7 +26619,7 @@
         <v>45036</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>45503</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>45448</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>45714</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>44997</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>45259</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>45520</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27135,7 +27135,7 @@
         <v>45119</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>45995</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>45996</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>45208</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         <v>45377</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>45239</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>46002</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>46007</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>45321</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>45646</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>44994</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45371</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>45231</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>44965</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>45264</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>45364</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>45197</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>45197</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>45096</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>45540</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>46020</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>46020</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>45162</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>45905</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>44895</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>46029</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>45446</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>46029</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>44910</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>46170</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>46170</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>46034</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>44951</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>46037</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29637,7 +29637,7 @@
         <v>44873</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29710,7 +29710,7 @@
         <v>45063</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>44557</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29856,7 +29856,7 @@
         <v>45436</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>45635</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>45079</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30080,7 +30080,7 @@
         <v>45002</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30153,7 +30153,7 @@
         <v>46176</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>46175</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45097</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>46176</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>46178</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>46180</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>46180</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>45301</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45078</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>46180</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>46076</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>44921</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>45110</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>46071</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>44802</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>45140</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>45733</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>46076</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>46183</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>45390</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>44505</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>46183</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>46079</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>45744</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31925,7 +31925,7 @@
         <v>46183</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>45147</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32071,7 +32071,7 @@
         <v>46089</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32144,7 +32144,7 @@
         <v>46089</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>45216</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32290,7 +32290,7 @@
         <v>44522</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>45195</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32436,7 +32436,7 @@
         <v>45195</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>45375</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>45572</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32655,7 +32655,7 @@
         <v>46189</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>46189</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32811,7 +32811,7 @@
         <v>46189</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>46189</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>46189</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>46189</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>46189</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33201,7 +33201,7 @@
         <v>46189</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>46189</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>46189</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33435,7 +33435,7 @@
         <v>46093</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         <v>46189</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>46189</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33664,7 +33664,7 @@
         <v>46100</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>46100</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33810,7 +33810,7 @@
         <v>45390</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>45588</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33961,7 +33961,7 @@
         <v>45117</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>46198</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>45573</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34190,7 +34190,7 @@
         <v>45016</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34268,7 +34268,7 @@
         <v>46199</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>44631</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>46200</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>45341</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>45362</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>46199</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44966</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45177</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45377</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>46126</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
         <v>45642</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>45555</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35154,7 +35154,7 @@
         <v>45453</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>45471</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35300,7 +35300,7 @@
         <v>45217</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35373,7 +35373,7 @@
         <v>46133</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35446,7 +35446,7 @@
         <v>46133</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>46133</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35592,7 +35592,7 @@
         <v>45686</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35665,7 +35665,7 @@
         <v>45370</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35738,7 +35738,7 @@
         <v>45628</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35811,7 +35811,7 @@
         <v>44557</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>45194</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35957,7 +35957,7 @@
         <v>44935</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>45035</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36103,7 +36103,7 @@
         <v>45237</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36176,7 +36176,7 @@
         <v>44620</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36254,7 +36254,7 @@
         <v>44620</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>44872</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>45908</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>45988</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>45071</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>45217</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>44487</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>44949</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>44957</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>45715</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36994,7 +36994,7 @@
         <v>46247</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>46205</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>45688</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37213,7 +37213,7 @@
         <v>45141</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>46253</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37359,7 +37359,7 @@
         <v>45093</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>45546</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37505,7 +37505,7 @@
         <v>44603</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>46210</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>45723</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>44823</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>45630</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44610</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>44530</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45483</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>46254</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38172,7 +38172,7 @@
         <v>45255</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>45117</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38318,7 +38318,7 @@
         <v>45537</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38391,7 +38391,7 @@
         <v>44804</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>45342</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>45342</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38610,7 +38610,7 @@
         <v>45011</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38683,7 +38683,7 @@
         <v>45071</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38756,7 +38756,7 @@
         <v>45422</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>44679</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38902,7 +38902,7 @@
         <v>45685</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>45105</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>46213</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39131,7 +39131,7 @@
         <v>46184</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>45314</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39277,7 +39277,7 @@
         <v>46213</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>45385</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>46265</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>45255</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>45217</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39652,7 +39652,7 @@
         <v>46265</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39730,7 +39730,7 @@
         <v>46265</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39808,7 +39808,7 @@
         <v>46265</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>46265</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39964,7 +39964,7 @@
         <v>46265</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>46265</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40120,7 +40120,7 @@
         <v>46265</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40198,7 +40198,7 @@
         <v>46265</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>44902</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>46266</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40427,7 +40427,7 @@
         <v>46266</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40500,7 +40500,7 @@
         <v>44957</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40573,7 +40573,7 @@
         <v>46267</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>45265</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40719,7 +40719,7 @@
         <v>46267</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>46268</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40865,7 +40865,7 @@
         <v>46268</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40938,7 +40938,7 @@
         <v>46268</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41011,7 +41011,7 @@
         <v>45453</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41084,7 +41084,7 @@
         <v>45035</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41157,7 +41157,7 @@
         <v>46268</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>45777</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41303,7 +41303,7 @@
         <v>45782</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41376,7 +41376,7 @@
         <v>46275</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41454,7 +41454,7 @@
         <v>45630</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41527,7 +41527,7 @@
         <v>45518</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>46276</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41683,7 +41683,7 @@
         <v>46276</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41761,7 +41761,7 @@
         <v>45702</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         <v>45721</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41907,7 +41907,7 @@
         <v>45474</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41980,7 +41980,7 @@
         <v>45719</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>44827</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>45708</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45737</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>46282</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45356</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>46282</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>45803</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>45471</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>45553</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42715,7 +42715,7 @@
         <v>45708</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42788,7 +42788,7 @@
         <v>45055</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45805</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>45635</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43007,7 +43007,7 @@
         <v>45834</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>45835</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43153,7 +43153,7 @@
         <v>45518</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45838</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>45838</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43377,7 +43377,7 @@
         <v>45826</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>45845</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43523,7 +43523,7 @@
         <v>45845</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45844</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>45744</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45867</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>45453</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45560</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43966,7 +43966,7 @@
         <v>44938</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>44656</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44112,7 +44112,7 @@
         <v>45476</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>44837</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>45264</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45400</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>45365</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44477,7 +44477,7 @@
         <v>45272</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45622</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44623,7 +44623,7 @@
         <v>44802</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>44802</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44769,7 +44769,7 @@
         <v>44820</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>45182</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>44806</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44988,7 +44988,7 @@
         <v>45453</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>44952</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45134,7 +45134,7 @@
         <v>44482</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45124</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>45350</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45353,7 +45353,7 @@
         <v>45370</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45426,7 +45426,7 @@
         <v>45373</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>44802</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>44635</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>45005</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>44719</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45791,7 +45791,7 @@
         <v>44938</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>45194</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>44805</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>44896</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>44622</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>45652</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46229,7 +46229,7 @@
         <v>45735</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46302,7 +46302,7 @@
         <v>45737</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46375,7 +46375,7 @@
         <v>45939</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46448,7 +46448,7 @@
         <v>45939</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46521,7 +46521,7 @@
         <v>45980</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>46030</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>46049</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46740,7 +46740,7 @@
         <v>46104</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46813,7 +46813,7 @@
         <v>46134</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46886,7 +46886,7 @@
         <v>46134</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>

--- a/Översikt OSBY.xlsx
+++ b/Översikt OSBY.xlsx
@@ -601,7 +601,7 @@
         <v>45589</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>46134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45177</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45844</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>44802</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>44827</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>46241</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>45796</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>46030</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>46134</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>46134</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>46153</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>44472</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45918</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>46153</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>45867</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>46189</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>45078</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>45607</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>45356</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>44622</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>44813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44722</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44788</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>45364</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>44902</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45905</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>45909</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>45925</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>44910</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>45999</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45799</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>45217</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45255</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>45126</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>46170</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>45002</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>44788</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>46178</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>46183</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>46189</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>45177</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>45117</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>44698</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>46275</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>45033</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>45649</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45272</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>45182</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44802</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45446</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>45735</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>44586</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>44553</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>44579</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44523</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>44472</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>44693</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44845</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>44869</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>44830</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>44603</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44827</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44523</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>44687</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44522</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>44650</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44813</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>44694</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>44746</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>44482</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>44481</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>44572</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>44813</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>44813</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>44529</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>44764</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>44762</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>44510</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>44510</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         <v>44478</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44575</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>44468</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>44595</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>44516</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>44505</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>44487</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>44806</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>44610</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         <v>44557</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>44731</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>44609</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>44843</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>44700</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>44469</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>44662</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>44830</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>44830</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>44831</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>44475</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>44823</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>44553</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44614</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>44788</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>44805</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>44623</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>44788</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>44834</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>44721</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>44610</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>44469</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>44573</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>44573</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>45483</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>45208</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>45390</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>45321</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         <v>45342</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>45342</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>45100</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>45371</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>45369</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>45035</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>44823</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>45217</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>45385</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44481</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>45093</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>45447</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>44804</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>44557</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>44557</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>45268</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>45471</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>45708</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>45884</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>46020</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>46020</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>44949</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>44895</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>45448</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45019</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45905</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>45436</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>45446</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>46029</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>46029</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>44522</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>45737</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>44827</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>45356</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>44921</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>46034</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>45434</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>45377</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>45884</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>46037</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>45548</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>45708</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>44610</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>45162</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>45902</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>45055</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>44994</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>45905</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>45097</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>45362</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>45908</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45909</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>44902</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>45553</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>45911</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>45911</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>45911</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>45911</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>45177</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>45744</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>44530</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>45912</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45506</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>44904</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>44881</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>45471</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>45803</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>45923</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>46071</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45572</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>46076</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>46079</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>45369</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>45930</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>45197</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>45805</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>45722</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>44965</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>44477</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>44524</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>44524</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>46089</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17431,7 +17431,7 @@
         <v>46089</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>45937</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>45937</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>45937</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44904</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>45071</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>44740</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>45937</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>46093</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>45390</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>45390</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>44610</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>45568</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>45364</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>45588</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>45231</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>46100</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>46100</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>45524</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>44662</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>45037</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>44679</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>45463</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>45964</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45369</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45035</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45635</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45964</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>46126</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>44602</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45971</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>45973</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45975</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>45607</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>45483</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>44997</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>45468</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>46133</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>46133</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>46133</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>45642</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>45982</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44801</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>45642</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45986</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45015</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>45091</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>45646</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>44757</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45520</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45908</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>45785</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>45988</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>45605</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>45605</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45666</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>45762</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44620</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>44620</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>45995</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45666</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>45996</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>45630</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22085,7 +22085,7 @@
         <v>44620</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>44505</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>46140</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45646</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>45733</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>45688</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>46002</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45714</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>45539</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>45635</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>45677</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>44832</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45154</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>46007</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23127,7 +23127,7 @@
         <v>45685</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45575</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>45737</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>45936</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>44746</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>45685</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>45377</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>44935</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45730</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45503</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45255</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45728</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>45537</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>45709</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>44994</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45012</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45264</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>44838</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45195</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>45195</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>44965</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>44790</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>45036</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>44910</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24904,7 +24904,7 @@
         <v>45255</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>45259</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>45117</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>45961</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>44900</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>46150</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>44749</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>45259</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>46153</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>46153</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25649,7 +25649,7 @@
         <v>44902</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>45834</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>46153</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>46153</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>45733</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>46153</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>46153</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>44895</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>46155</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>45915</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>45835</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>45838</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>46155</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>45838</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>44826</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>45360</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>45518</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26910,7 +26910,7 @@
         <v>45723</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>45211</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>46079</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>44872</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>45826</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>44921</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>45107</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         <v>45845</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45844</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>45845</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>45238</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>45240</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>45015</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>45082</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45141</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>45744</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28088,7 +28088,7 @@
         <v>45110</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>46170</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>46170</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>45002</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45404</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>45589</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>45078</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>45078</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>46175</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>44557</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>45867</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>44511</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>46176</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>44529</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>46076</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>46176</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>46180</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>46180</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>46178</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>45096</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>45630</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>45063</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29709,7 +29709,7 @@
         <v>44966</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44867</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>46180</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29933,7 +29933,7 @@
         <v>46183</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>46183</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>46183</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>45141</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>45175</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30298,7 +30298,7 @@
         <v>45656</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         <v>45162</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30444,7 +30444,7 @@
         <v>45643</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30517,7 +30517,7 @@
         <v>45117</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>45453</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         <v>46189</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30751,7 +30751,7 @@
         <v>46189</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30829,7 +30829,7 @@
         <v>46189</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>46189</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>46189</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>46189</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>46189</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>46189</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>46189</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>46189</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45011</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>46189</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>45471</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>46189</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>44585</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>45534</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>45534</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>45217</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>45035</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>44832</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>46198</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>46199</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>44644</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32427,7 +32427,7 @@
         <v>46200</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>46199</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>45706</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32646,7 +32646,7 @@
         <v>44658</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>46205</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>45196</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>44585</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32943,7 +32943,7 @@
         <v>45119</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>45453</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>46210</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>45695</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>45609</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>46253</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>46254</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>46213</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>45148</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>44663</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>45666</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>45140</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33819,7 +33819,7 @@
         <v>45715</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>46213</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45686</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45209</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>46184</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>44776</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>45194</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>45422</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>45631</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>45110</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>45197</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>45197</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>45301</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>45231</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>44790</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>46266</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>46265</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>46265</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>46266</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>46265</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35299,7 +35299,7 @@
         <v>46265</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>46265</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45314</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>46265</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>46265</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>46265</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>46265</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44802</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>45265</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>46267</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>46268</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>46268</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>46267</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36278,7 +36278,7 @@
         <v>46268</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>46268</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36424,7 +36424,7 @@
         <v>45237</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36497,7 +36497,7 @@
         <v>45216</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36570,7 +36570,7 @@
         <v>45555</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>46276</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44873</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>46275</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>45733</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>46276</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>44603</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>45147</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45610</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>44978</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37325,7 +37325,7 @@
         <v>45652</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>44911</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>46282</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         <v>46282</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37617,7 +37617,7 @@
         <v>45342</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44585</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>44580</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37836,7 +37836,7 @@
         <v>45436</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37909,7 +37909,7 @@
         <v>44916</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>44951</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>45414</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>44951</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38201,7 +38201,7 @@
         <v>44742</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>44845</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>45573</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>45555</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38493,7 +38493,7 @@
         <v>44957</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>44631</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>46290</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38722,7 +38722,7 @@
         <v>46247</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>45016</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>46289</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>46289</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39024,7 +39024,7 @@
         <v>45239</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>45341</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45436</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>44487</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45071</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39389,7 +39389,7 @@
         <v>45097</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>44711</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>45282</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>45632</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45243</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45217</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45079</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>45011</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>45237</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40051,7 +40051,7 @@
         <v>45037</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45546</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>44743</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>45375</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>44904</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45036</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45453</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>44594</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>44783</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>45573</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>45589</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45589</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>45370</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45119</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>44904</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>45683</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>45141</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41292,7 +41292,7 @@
         <v>45105</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>45353</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>45443</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>45537</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>45063</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>45273</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>45628</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>45648</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>45033</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>45231</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45154</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>45453</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>44903</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42251,7 +42251,7 @@
         <v>44957</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>45062</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>45208</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>45323</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>45362</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45540</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>45686</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>45093</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42840,7 +42840,7 @@
         <v>45506</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>45404</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>45777</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43059,7 +43059,7 @@
         <v>45782</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
         <v>45518</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43210,7 +43210,7 @@
         <v>45702</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>45721</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>45474</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>45630</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>45719</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43575,7 +43575,7 @@
         <v>44656</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43648,7 +43648,7 @@
         <v>44635</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>44719</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43794,7 +43794,7 @@
         <v>44622</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43867,7 +43867,7 @@
         <v>45560</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43940,7 +43940,7 @@
         <v>44938</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45476</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44086,7 +44086,7 @@
         <v>44837</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>45264</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45400</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>45365</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44378,7 +44378,7 @@
         <v>45272</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45622</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>44802</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>44802</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44670,7 +44670,7 @@
         <v>44820</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44743,7 +44743,7 @@
         <v>45182</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>44806</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>45453</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>44952</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>44482</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45124</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>45350</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>45370</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>45373</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45400,7 +45400,7 @@
         <v>44802</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45473,7 +45473,7 @@
         <v>45005</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>44938</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45619,7 +45619,7 @@
         <v>45194</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>44805</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45765,7 +45765,7 @@
         <v>44896</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45652</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         <v>45735</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45984,7 +45984,7 @@
         <v>45737</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46057,7 +46057,7 @@
         <v>45939</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>45939</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46203,7 +46203,7 @@
         <v>45980</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46276,7 +46276,7 @@
         <v>46030</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>46049</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46422,7 +46422,7 @@
         <v>46104</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46495,7 +46495,7 @@
         <v>46134</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>46134</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>

--- a/Översikt OSBY.xlsx
+++ b/Översikt OSBY.xlsx
@@ -601,7 +601,7 @@
         <v>45589</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>46134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45177</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45844</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>44802</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>44827</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>46241</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>45796</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>46030</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>46134</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>46134</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>46153</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>44472</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45918</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>46153</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>45867</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>46189</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>45078</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>45607</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>45356</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>44622</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>44813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44722</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44788</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>45364</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>44902</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45905</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>45909</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>45925</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>44910</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>45999</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45799</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>45217</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45255</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>45126</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>46170</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>45002</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>44788</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>46178</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>46183</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>46189</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>45177</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>45117</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>44698</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>46275</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>45033</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>45649</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45272</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>45182</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44802</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45446</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>45735</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>44586</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>44553</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>44579</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44523</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>44472</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>44693</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44845</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>44869</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>44830</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>44603</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44827</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44523</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>44687</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44522</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>44650</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44813</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>44694</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>44746</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>44482</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>44481</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>44572</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>44813</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>44813</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>44529</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>44764</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>44762</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>44510</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>44510</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         <v>44478</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44575</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>44468</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>44595</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>44516</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>44505</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>44487</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>44806</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>44610</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         <v>44557</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>44731</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>44609</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>44843</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>44700</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>44469</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>44662</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>44830</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>44830</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>44831</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>44475</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>44823</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>44553</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44614</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>44788</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>44805</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>44623</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>44788</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>44834</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>44721</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>44610</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>44469</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>44573</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>44573</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>45483</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>45208</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>45390</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>45321</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         <v>45342</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>45342</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>45100</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>45371</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>45369</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>45035</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>44823</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>45217</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>45385</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44481</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>45093</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>45447</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>44804</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>44557</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>44557</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>45268</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>45471</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>45708</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>45884</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>46020</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>46020</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>44949</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>44895</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>45448</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45019</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45905</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>45436</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>45446</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>46029</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>46029</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>44522</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>45737</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>44827</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>45356</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>44921</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>46034</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>45434</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>45377</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>45884</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>46037</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>45548</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>45708</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>44610</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>45162</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>45902</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>45055</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>44994</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>45905</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>45097</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>45362</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>45908</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45909</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>44902</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>45553</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>45911</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>45911</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>45911</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>45911</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>45177</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>45744</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>44530</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>45912</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45506</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>44904</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>44881</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>45471</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>45803</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>45923</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>46071</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45572</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>46076</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>46079</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>45369</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>45930</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>45197</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>45805</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>45722</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>44965</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>44477</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>44524</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>44524</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>46089</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17431,7 +17431,7 @@
         <v>46089</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>45937</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>45937</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>45937</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44904</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>45071</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>44740</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>45937</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>46093</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>45390</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>45390</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>44610</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>45568</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>45364</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>45588</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>45231</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>46100</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>46100</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>45524</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>44662</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>45037</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>44679</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>45463</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>45964</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45369</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45035</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45635</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45964</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>46126</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>44602</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45971</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>45973</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45975</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>45607</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>45483</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>44997</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>45468</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>46133</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>46133</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>46133</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>45642</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>45982</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44801</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>45642</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45986</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45015</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>45091</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>45646</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>44757</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45520</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45908</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>45785</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>45988</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>45605</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>45605</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45666</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>45762</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44620</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>44620</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>45995</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45666</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>45996</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>45630</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22085,7 +22085,7 @@
         <v>44620</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>44505</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>46140</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45646</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>45733</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>45688</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>46002</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45714</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>45539</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>45635</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>45677</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>44832</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45154</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>46007</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23127,7 +23127,7 @@
         <v>45685</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45575</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>45737</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>45936</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>44746</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>45685</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>45377</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>44935</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45730</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45503</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45255</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45728</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>45537</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>45709</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>44994</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45012</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45264</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>44838</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45195</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>45195</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>44965</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>44790</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>45036</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>44910</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24904,7 +24904,7 @@
         <v>45255</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>45259</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>45117</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>45961</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>44900</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>46150</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>44749</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>45259</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>46153</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>46153</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25649,7 +25649,7 @@
         <v>44902</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>45834</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>46153</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>46153</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>45733</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>46153</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>46153</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>44895</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>46155</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>45915</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>45835</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>45838</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>46155</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>45838</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>44826</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>45360</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>45518</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26910,7 +26910,7 @@
         <v>45723</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>45211</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>46079</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>44872</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>45826</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>44921</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>45107</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         <v>45845</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45844</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>45845</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>45238</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>45240</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>45015</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>45082</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45141</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>45744</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28088,7 +28088,7 @@
         <v>45110</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>46170</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>46170</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>45002</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45404</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>45589</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>45078</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>45078</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>46175</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>44557</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>45867</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>44511</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>46176</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>44529</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>46076</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>46176</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>46180</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>46180</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>46178</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>45096</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>45630</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>45063</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29709,7 +29709,7 @@
         <v>44966</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44867</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>46180</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29933,7 +29933,7 @@
         <v>46183</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>46183</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>46183</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>45141</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>45175</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30298,7 +30298,7 @@
         <v>45656</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         <v>45162</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30444,7 +30444,7 @@
         <v>45643</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30517,7 +30517,7 @@
         <v>45117</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>45453</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         <v>46189</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30751,7 +30751,7 @@
         <v>46189</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30829,7 +30829,7 @@
         <v>46189</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>46189</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>46189</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>46189</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>46189</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>46189</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>46189</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>46189</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45011</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>46189</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>45471</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>46189</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>44585</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>45534</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>45534</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>45217</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>45035</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>44832</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>46198</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>46199</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>44644</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32427,7 +32427,7 @@
         <v>46200</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>46199</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>45706</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32646,7 +32646,7 @@
         <v>44658</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>46205</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>45196</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>44585</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32943,7 +32943,7 @@
         <v>45119</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>45453</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>46210</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>45695</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>45609</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>46253</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>46254</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>46213</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>45148</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>44663</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>45666</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>45140</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33819,7 +33819,7 @@
         <v>45715</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>46213</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45686</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45209</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>46184</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>44776</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>45194</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>45422</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>45631</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>45110</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>45197</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>45197</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>45301</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>45231</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>44790</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>46266</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>46265</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>46265</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>46266</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>46265</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35299,7 +35299,7 @@
         <v>46265</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>46265</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45314</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>46265</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>46265</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>46265</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>46265</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>44802</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>45265</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>46267</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>46268</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>46268</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>46267</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36278,7 +36278,7 @@
         <v>46268</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>46268</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36424,7 +36424,7 @@
         <v>45237</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36497,7 +36497,7 @@
         <v>45216</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36570,7 +36570,7 @@
         <v>45555</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>46276</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44873</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>46275</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>45733</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>46276</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>44603</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>45147</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45610</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>44978</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37325,7 +37325,7 @@
         <v>45652</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>44911</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>46282</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         <v>46282</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37617,7 +37617,7 @@
         <v>45342</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44585</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>44580</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37836,7 +37836,7 @@
         <v>45436</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37909,7 +37909,7 @@
         <v>44916</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>44951</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>45414</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>44951</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38201,7 +38201,7 @@
         <v>44742</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>44845</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>45573</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>45555</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38493,7 +38493,7 @@
         <v>44957</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>44631</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>46290</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38722,7 +38722,7 @@
         <v>46247</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>45016</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>46289</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>46289</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39024,7 +39024,7 @@
         <v>45239</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>45341</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45436</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>44487</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45071</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39389,7 +39389,7 @@
         <v>45097</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>44711</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>45282</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>45632</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45243</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45217</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45079</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>45011</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>45237</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40051,7 +40051,7 @@
         <v>45037</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45546</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>44743</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>45375</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>44904</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45036</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45453</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>44594</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>44783</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>45573</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>45589</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45589</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>45370</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45119</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>44904</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>45683</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>45141</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41292,7 +41292,7 @@
         <v>45105</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>45353</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>45443</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>45537</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>45063</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>45273</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>45628</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>45648</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>45033</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>45231</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45154</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>45453</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>44903</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42251,7 +42251,7 @@
         <v>44957</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>45062</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>45208</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>45323</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>45362</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45540</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>45686</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>45093</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42840,7 +42840,7 @@
         <v>45506</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>45404</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>45777</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43059,7 +43059,7 @@
         <v>45782</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
         <v>45518</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43210,7 +43210,7 @@
         <v>45702</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>45721</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>45474</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>45630</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>45719</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43575,7 +43575,7 @@
         <v>44656</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43648,7 +43648,7 @@
         <v>44635</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>44719</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43794,7 +43794,7 @@
         <v>44622</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43867,7 +43867,7 @@
         <v>45560</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43940,7 +43940,7 @@
         <v>44938</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45476</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44086,7 +44086,7 @@
         <v>44837</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>45264</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45400</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>45365</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44378,7 +44378,7 @@
         <v>45272</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45622</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>44802</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>44802</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44670,7 +44670,7 @@
         <v>44820</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44743,7 +44743,7 @@
         <v>45182</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>44806</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>45453</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>44952</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>44482</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45124</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>45350</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>45370</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>45373</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45400,7 +45400,7 @@
         <v>44802</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45473,7 +45473,7 @@
         <v>45005</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>44938</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45619,7 +45619,7 @@
         <v>45194</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>44805</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45765,7 +45765,7 @@
         <v>44896</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45652</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         <v>45735</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45984,7 +45984,7 @@
         <v>45737</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46057,7 +46057,7 @@
         <v>45939</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>45939</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46203,7 +46203,7 @@
         <v>45980</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46276,7 +46276,7 @@
         <v>46030</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>46049</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46422,7 +46422,7 @@
         <v>46104</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46495,7 +46495,7 @@
         <v>46134</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>46134</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>

--- a/Översikt OSBY.xlsx
+++ b/Översikt OSBY.xlsx
@@ -601,7 +601,7 @@
         <v>45589</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>46134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45177</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45844</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>44802</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>44827</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>46241</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>45796</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>46030</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>46134</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>46134</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>46153</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>44472</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45356</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>45918</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>45867</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>46153</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>46189</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>45078</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>46295</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>45607</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44622</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>44813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>44852</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>44722</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>44788</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45117</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>45905</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45909</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44902</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>45925</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>45177</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>45033</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45999</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>45217</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>45799</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>44788</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>46170</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>46178</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>46183</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46189</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>45002</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>45364</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>46275</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>45126</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>44698</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>45255</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>44910</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>45649</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>45272</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>45182</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45446</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45735</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>44586</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>44553</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>44523</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>44579</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>44472</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>44693</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44845</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44869</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>44830</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>44603</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>44523</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>44827</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>44522</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>44687</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>44650</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>44813</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44694</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>44746</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>44482</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>44481</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>44572</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>44813</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>44813</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>44529</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>44764</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>44762</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>44510</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>44510</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>44478</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44575</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>44595</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>44487</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>44516</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>44505</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>44806</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>44731</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
         <v>44610</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44557</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>44843</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>44609</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>44700</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>44662</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>44830</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>44830</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>44831</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>44475</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>44823</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>44553</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>44614</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>44788</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>44805</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>44623</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>44788</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         <v>44721</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>44834</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>44610</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>44573</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>44573</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>45447</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>45369</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>45453</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>45607</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>44881</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>44900</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>44965</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>45078</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>45063</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>45196</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>44895</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>44994</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>45259</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
         <v>45709</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>45268</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>45702</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>45035</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>45666</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>45238</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>45037</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>45015</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>44790</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>45721</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>44740</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>45019</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>45097</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>45884</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>46002</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45643</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>45474</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45652</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>46007</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>45719</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>45573</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>45231</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>45231</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>45353</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>45884</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>45605</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45605</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>45211</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>45728</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>44904</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>44904</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>45506</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>46020</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>46020</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>44585</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>45905</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>44594</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>46029</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>45733</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>46029</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>45646</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>46034</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>45902</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>46037</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>45555</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>45905</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>45209</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>44662</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>45908</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>45631</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>45909</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>45362</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>44904</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>45911</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>45911</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>45911</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>45911</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>44827</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45708</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>45737</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>45912</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>45722</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>45356</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>45803</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>45471</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>45553</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>45708</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>45055</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>45805</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>45923</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>44921</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>45568</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>45548</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>45683</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>44585</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>45930</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>44903</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>45685</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>45937</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45937</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>45937</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>46071</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>45937</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44832</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>44481</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>46076</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>46079</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45609</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45110</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>45062</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>44585</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>45471</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>44826</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45537</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>44742</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>46089</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>44602</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45243</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>46089</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45093</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45082</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>44580</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45036</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44801</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>45964</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45463</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>45730</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>45240</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45964</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>45483</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>44749</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>46093</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>44916</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>45468</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>45015</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>45404</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>44867</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>44663</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>45973</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>45971</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>46100</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>46100</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>45656</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45273</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>45975</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45666</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>45033</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45037</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>44743</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45635</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>45107</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45982</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45524</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>44529</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44746</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>44832</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45986</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>44783</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45162</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>44511</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>44978</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>45520</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>44757</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>46126</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>45323</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>45995</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         <v>45996</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
         <v>44951</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22856,7 +22856,7 @@
         <v>45369</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>45175</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>46133</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>45642</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>46133</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>46133</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23294,7 +23294,7 @@
         <v>45390</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>45100</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>45141</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23518,7 +23518,7 @@
         <v>44644</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>45342</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>45436</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>45695</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45834</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45835</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>45632</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>44935</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>45534</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>45534</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>45141</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>45518</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>45838</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>45838</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>44845</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>44620</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45826</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>44620</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45908</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>45677</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>45988</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45762</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>45845</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>45845</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>45844</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>45154</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25431,7 +25431,7 @@
         <v>44711</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44524</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>44524</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>45539</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>45785</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44620</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>44477</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>44776</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>45282</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>44790</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26171,7 +26171,7 @@
         <v>45666</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>45589</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>45589</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>45686</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44904</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>45744</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>45936</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>45011</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>45414</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26828,7 +26828,7 @@
         <v>45506</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26901,7 +26901,7 @@
         <v>45091</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>44902</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>45434</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45648</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>45119</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>44838</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>45575</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45867</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>45589</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45197</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>45453</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>45610</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>45737</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>45012</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>45961</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>44658</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>45369</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>46153</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>46150</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>46153</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28386,7 +28386,7 @@
         <v>46153</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>46153</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28542,7 +28542,7 @@
         <v>45733</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>46153</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>46155</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>46153</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45915</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45237</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>45360</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>45148</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>46155</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>46079</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>44557</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29355,7 +29355,7 @@
         <v>45404</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>45154</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>44911</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29574,7 +29574,7 @@
         <v>45208</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>45436</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>45706</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>45630</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29866,7 +29866,7 @@
         <v>46170</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>46170</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>44610</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>45443</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>45036</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>45503</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>46176</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>46175</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>46176</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>46178</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>46180</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>46180</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>45448</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>45714</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>46180</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>46076</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31054,7 +31054,7 @@
         <v>44997</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31127,7 +31127,7 @@
         <v>45259</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>46183</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31273,7 +31273,7 @@
         <v>45119</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>46183</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>45208</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>46183</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>45377</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>46189</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>46189</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>46189</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31877,7 +31877,7 @@
         <v>46189</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>46189</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>46189</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45239</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>46189</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32262,7 +32262,7 @@
         <v>46189</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>46189</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32418,7 +32418,7 @@
         <v>46189</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45321</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>46189</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32647,7 +32647,7 @@
         <v>46189</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>45646</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>44994</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>45371</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>45231</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44965</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>45264</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>45364</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>46198</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33314,7 +33314,7 @@
         <v>45197</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33387,7 +33387,7 @@
         <v>45197</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33460,7 +33460,7 @@
         <v>45096</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>45540</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>46199</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>46200</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>46199</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33830,7 +33830,7 @@
         <v>45162</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>44895</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>45446</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>44910</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>46205</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>44951</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>44873</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>46210</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>45063</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>44557</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>45436</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>46213</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>46184</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45635</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45079</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>45002</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>46213</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45097</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>45301</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>45078</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>46265</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>46265</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>46265</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>46265</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>46265</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>46265</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>46265</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>46265</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35929,7 +35929,7 @@
         <v>46265</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36007,7 +36007,7 @@
         <v>46266</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36080,7 +36080,7 @@
         <v>46266</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36153,7 +36153,7 @@
         <v>44921</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>45110</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>46267</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>46267</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36445,7 +36445,7 @@
         <v>46268</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36518,7 +36518,7 @@
         <v>46268</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>46268</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>46268</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36737,7 +36737,7 @@
         <v>44802</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36810,7 +36810,7 @@
         <v>45140</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36883,7 +36883,7 @@
         <v>45733</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36956,7 +36956,7 @@
         <v>45390</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>44505</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37107,7 +37107,7 @@
         <v>45744</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37180,7 +37180,7 @@
         <v>45147</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37253,7 +37253,7 @@
         <v>46275</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37331,7 +37331,7 @@
         <v>46276</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
         <v>46276</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>45216</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37560,7 +37560,7 @@
         <v>44522</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>45195</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37706,7 +37706,7 @@
         <v>45195</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37779,7 +37779,7 @@
         <v>45375</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37852,7 +37852,7 @@
         <v>45572</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>46282</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>46282</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>45390</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38149,7 +38149,7 @@
         <v>45588</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>45117</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38300,7 +38300,7 @@
         <v>45573</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>45016</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38451,7 +38451,7 @@
         <v>46289</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38524,7 +38524,7 @@
         <v>44631</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>45341</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>45362</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>46289</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
         <v>44966</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38904,7 +38904,7 @@
         <v>45177</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38977,7 +38977,7 @@
         <v>45377</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39050,7 +39050,7 @@
         <v>45642</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39123,7 +39123,7 @@
         <v>46290</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>45555</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>45453</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>45471</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>45217</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>45686</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39566,7 +39566,7 @@
         <v>45370</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>45628</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>44557</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39785,7 +39785,7 @@
         <v>45194</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39858,7 +39858,7 @@
         <v>45035</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39931,7 +39931,7 @@
         <v>45237</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>44872</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45071</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>45217</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>44487</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>44949</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>44957</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>46254</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40520,7 +40520,7 @@
         <v>45715</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40593,7 +40593,7 @@
         <v>46253</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>46247</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>45688</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>45141</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40885,7 +40885,7 @@
         <v>45093</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40958,7 +40958,7 @@
         <v>45546</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         <v>44603</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>45723</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>44823</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>45630</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41323,7 +41323,7 @@
         <v>44610</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41396,7 +41396,7 @@
         <v>44530</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41474,7 +41474,7 @@
         <v>45483</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41552,7 +41552,7 @@
         <v>45255</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41625,7 +41625,7 @@
         <v>45117</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>45537</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41771,7 +41771,7 @@
         <v>44804</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>45342</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>45342</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41990,7 +41990,7 @@
         <v>45011</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>45071</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42136,7 +42136,7 @@
         <v>45422</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42209,7 +42209,7 @@
         <v>44679</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42282,7 +42282,7 @@
         <v>45685</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45105</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>45314</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         <v>45385</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>45255</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>45217</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42730,7 +42730,7 @@
         <v>44902</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>44957</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>45265</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42954,7 +42954,7 @@
         <v>45453</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43027,7 +43027,7 @@
         <v>45035</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43100,7 +43100,7 @@
         <v>45777</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43173,7 +43173,7 @@
         <v>45782</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43246,7 +43246,7 @@
         <v>45630</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>45518</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>45560</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43470,7 +43470,7 @@
         <v>44938</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>44656</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43616,7 +43616,7 @@
         <v>45476</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>44837</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43762,7 +43762,7 @@
         <v>45264</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45400</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>45365</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43981,7 +43981,7 @@
         <v>45272</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44054,7 +44054,7 @@
         <v>45622</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>44802</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44200,7 +44200,7 @@
         <v>44802</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>44820</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>45182</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>44806</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44492,7 +44492,7 @@
         <v>45453</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>44952</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>44482</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>45124</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>45350</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
         <v>45370</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>45373</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>44802</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>44635</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>45005</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>44719</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45295,7 +45295,7 @@
         <v>44938</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>45194</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45441,7 +45441,7 @@
         <v>44805</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>44896</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45587,7 +45587,7 @@
         <v>44622</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45652</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45733,7 +45733,7 @@
         <v>45735</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45737</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45939</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45939</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45980</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46098,7 +46098,7 @@
         <v>46030</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>46049</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>46104</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>46134</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46390,7 +46390,7 @@
         <v>46134</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>

--- a/Översikt OSBY.xlsx
+++ b/Översikt OSBY.xlsx
@@ -601,7 +601,7 @@
         <v>45589</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>46134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45177</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45844</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>44802</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>44827</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>46241</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>45796</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>46030</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>46134</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>46134</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>46153</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>44472</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45356</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>45918</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>45867</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>46153</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>46189</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>45078</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>46295</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>45607</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>44622</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>44813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>44852</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>44722</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>44788</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45117</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>45905</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45909</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44902</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>45925</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>45177</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>45033</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45999</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>45217</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>45799</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>44788</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>46170</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>46178</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>46183</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46189</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>45002</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>45364</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>46275</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>45126</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>44698</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>45255</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>44910</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>45649</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>45272</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>45182</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45446</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45735</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>44586</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>44553</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>44523</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>44579</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>44472</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>44693</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44845</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44869</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>44830</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>44603</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>44523</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>44827</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>44522</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>44687</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>44650</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>44813</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44694</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>44746</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>44482</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>44481</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>44572</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>44813</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>44813</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>44529</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>44764</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>44762</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>44510</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>44510</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>44478</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44575</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>44595</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>44487</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>44516</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>44505</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>44806</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>44731</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
         <v>44610</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44557</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>44843</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>44609</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>44700</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>44662</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>44830</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>44830</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>44831</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>44475</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>44823</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>44553</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>44614</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>44788</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>44805</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>44623</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>44788</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         <v>44721</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>44834</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>44610</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>44573</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>44573</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>45447</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>45369</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>45453</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>45607</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>44881</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>44900</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>44965</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>45078</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>45063</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>45196</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>44895</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>44994</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>45259</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
         <v>45709</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>45268</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>45702</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>45035</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>45666</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>45238</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>45037</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>45015</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>44790</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>45721</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>44740</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>45019</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>45097</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>45884</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>46002</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45643</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>45474</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45652</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>46007</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>45719</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>45573</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>45231</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>45231</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>45353</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>45884</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>45605</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45605</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>45211</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>45728</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>44904</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>44904</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>45506</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>46020</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>46020</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>44585</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>45905</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>44594</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>46029</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>45733</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>46029</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>45646</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>46034</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>45902</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>46037</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>45555</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>45905</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>45209</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>44662</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>45908</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>45631</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>45909</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>45362</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>44904</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>45911</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>45911</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>45911</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>45911</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>44827</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45708</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>45737</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>45912</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>45722</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>45356</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>45803</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>45471</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>45553</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>45708</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>45055</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>45805</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>45923</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>44921</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>45568</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>45548</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>45683</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>44585</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>45930</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>44903</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>45685</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>45937</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45937</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>45937</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>46071</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>45937</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44832</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>44481</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>46076</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>46079</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45609</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45110</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>45062</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>44585</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>45471</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>44826</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45537</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>44742</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>46089</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>44602</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45243</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>46089</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45093</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45082</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>44580</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45036</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44801</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>45964</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45463</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>45730</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>45240</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45964</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>45483</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>44749</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>46093</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>44916</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>45468</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>45015</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>45404</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>44867</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>44663</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>45973</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>45971</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>46100</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>46100</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>45656</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45273</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>45975</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45666</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>45033</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45037</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>44743</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45635</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>45107</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45982</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45524</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>44529</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44746</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>44832</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45986</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>44783</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45162</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>44511</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>44978</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>45520</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>44757</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>46126</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>45323</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>45995</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         <v>45996</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
         <v>44951</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22856,7 +22856,7 @@
         <v>45369</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>45175</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>46133</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>45642</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>46133</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>46133</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23294,7 +23294,7 @@
         <v>45390</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>45100</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>45141</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23518,7 +23518,7 @@
         <v>44644</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>45342</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>45436</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>45695</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45834</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45835</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>45632</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>44935</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>45534</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>45534</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>45141</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>45518</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>45838</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>45838</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>44845</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>44620</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45826</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>44620</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45908</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>45677</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>45988</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45762</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>45845</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>45845</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>45844</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>45154</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25431,7 +25431,7 @@
         <v>44711</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44524</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>44524</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>45539</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>45785</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44620</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>44477</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>44776</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>45282</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>44790</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26171,7 +26171,7 @@
         <v>45666</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>45589</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>45589</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>45686</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44904</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>45744</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>45936</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>45011</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>45414</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26828,7 +26828,7 @@
         <v>45506</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26901,7 +26901,7 @@
         <v>45091</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>44902</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>45434</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45648</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>45119</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>44838</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>45575</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45867</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>45589</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45197</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>45453</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>45610</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>45737</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>45012</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>45961</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>44658</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>45369</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>46153</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>46150</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>46153</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28386,7 +28386,7 @@
         <v>46153</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>46153</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28542,7 +28542,7 @@
         <v>45733</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>46153</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>46155</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>46153</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45915</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45237</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>45360</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>45148</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>46155</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>46079</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>44557</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29355,7 +29355,7 @@
         <v>45404</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>45154</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>44911</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29574,7 +29574,7 @@
         <v>45208</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>45436</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>45706</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>45630</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29866,7 +29866,7 @@
         <v>46170</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>46170</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>44610</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>45443</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>45036</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>45503</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>46176</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>46175</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>46176</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>46178</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>46180</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>46180</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>45448</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>45714</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>46180</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>46076</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31054,7 +31054,7 @@
         <v>44997</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31127,7 +31127,7 @@
         <v>45259</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>46183</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31273,7 +31273,7 @@
         <v>45119</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>46183</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>45208</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>46183</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>45377</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>46189</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>46189</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>46189</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31877,7 +31877,7 @@
         <v>46189</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>46189</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>46189</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45239</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>46189</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32262,7 +32262,7 @@
         <v>46189</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>46189</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32418,7 +32418,7 @@
         <v>46189</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45321</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>46189</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32647,7 +32647,7 @@
         <v>46189</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>45646</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>44994</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>45371</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>45231</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44965</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>45264</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>45364</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>46198</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33314,7 +33314,7 @@
         <v>45197</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33387,7 +33387,7 @@
         <v>45197</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33460,7 +33460,7 @@
         <v>45096</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>45540</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>46199</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>46200</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>46199</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33830,7 +33830,7 @@
         <v>45162</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>44895</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>45446</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>44910</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>46205</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>44951</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>44873</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>46210</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>45063</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>44557</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>45436</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>46213</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>46184</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45635</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45079</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>45002</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>46213</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45097</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>45301</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>45078</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>46265</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>46265</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>46265</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>46265</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>46265</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>46265</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>46265</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>46265</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35929,7 +35929,7 @@
         <v>46265</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36007,7 +36007,7 @@
         <v>46266</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36080,7 +36080,7 @@
         <v>46266</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36153,7 +36153,7 @@
         <v>44921</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>45110</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>46267</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>46267</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36445,7 +36445,7 @@
         <v>46268</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36518,7 +36518,7 @@
         <v>46268</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>46268</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>46268</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36737,7 +36737,7 @@
         <v>44802</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36810,7 +36810,7 @@
         <v>45140</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36883,7 +36883,7 @@
         <v>45733</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36956,7 +36956,7 @@
         <v>45390</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>44505</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37107,7 +37107,7 @@
         <v>45744</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37180,7 +37180,7 @@
         <v>45147</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37253,7 +37253,7 @@
         <v>46275</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37331,7 +37331,7 @@
         <v>46276</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
         <v>46276</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>45216</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37560,7 +37560,7 @@
         <v>44522</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>45195</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37706,7 +37706,7 @@
         <v>45195</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37779,7 +37779,7 @@
         <v>45375</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37852,7 +37852,7 @@
         <v>45572</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>46282</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>46282</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>45390</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38149,7 +38149,7 @@
         <v>45588</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>45117</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38300,7 +38300,7 @@
         <v>45573</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>45016</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38451,7 +38451,7 @@
         <v>46289</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38524,7 +38524,7 @@
         <v>44631</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>45341</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>45362</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>46289</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
         <v>44966</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38904,7 +38904,7 @@
         <v>45177</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38977,7 +38977,7 @@
         <v>45377</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39050,7 +39050,7 @@
         <v>45642</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39123,7 +39123,7 @@
         <v>46290</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>45555</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>45453</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>45471</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>45217</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>45686</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39566,7 +39566,7 @@
         <v>45370</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>45628</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>44557</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39785,7 +39785,7 @@
         <v>45194</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39858,7 +39858,7 @@
         <v>45035</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39931,7 +39931,7 @@
         <v>45237</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>44872</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45071</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>45217</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>44487</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>44949</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>44957</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>46254</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40520,7 +40520,7 @@
         <v>45715</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40593,7 +40593,7 @@
         <v>46253</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>46247</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>45688</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>45141</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40885,7 +40885,7 @@
         <v>45093</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40958,7 +40958,7 @@
         <v>45546</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         <v>44603</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>45723</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>44823</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>45630</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41323,7 +41323,7 @@
         <v>44610</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41396,7 +41396,7 @@
         <v>44530</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41474,7 +41474,7 @@
         <v>45483</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41552,7 +41552,7 @@
         <v>45255</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41625,7 +41625,7 @@
         <v>45117</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>45537</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41771,7 +41771,7 @@
         <v>44804</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>45342</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>45342</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41990,7 +41990,7 @@
         <v>45011</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>45071</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42136,7 +42136,7 @@
         <v>45422</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42209,7 +42209,7 @@
         <v>44679</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42282,7 +42282,7 @@
         <v>45685</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45105</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>45314</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         <v>45385</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>45255</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>45217</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42730,7 +42730,7 @@
         <v>44902</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>44957</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>45265</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42954,7 +42954,7 @@
         <v>45453</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43027,7 +43027,7 @@
         <v>45035</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43100,7 +43100,7 @@
         <v>45777</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43173,7 +43173,7 @@
         <v>45782</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43246,7 +43246,7 @@
         <v>45630</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>45518</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>45560</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43470,7 +43470,7 @@
         <v>44938</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>44656</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43616,7 +43616,7 @@
         <v>45476</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>44837</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43762,7 +43762,7 @@
         <v>45264</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45400</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>45365</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43981,7 +43981,7 @@
         <v>45272</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44054,7 +44054,7 @@
         <v>45622</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>44802</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44200,7 +44200,7 @@
         <v>44802</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>44820</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>45182</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>44806</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44492,7 +44492,7 @@
         <v>45453</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>44952</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>44482</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>45124</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>45350</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
         <v>45370</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>45373</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>44802</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>44635</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>45005</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>44719</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45295,7 +45295,7 @@
         <v>44938</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>45194</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45441,7 +45441,7 @@
         <v>44805</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>44896</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45587,7 +45587,7 @@
         <v>44622</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45652</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45733,7 +45733,7 @@
         <v>45735</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45737</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45939</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45939</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45980</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46098,7 +46098,7 @@
         <v>46030</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>46049</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>46104</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>46134</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46390,7 +46390,7 @@
         <v>46134</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>

--- a/Översikt OSBY.xlsx
+++ b/Översikt OSBY.xlsx
@@ -601,7 +601,7 @@
         <v>45589</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>46134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45177</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45844</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>44802</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>44827</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>46241</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>45796</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>46030</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>46134</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>46134</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>46153</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>45356</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45078</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>45607</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>45867</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>45918</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>46153</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>46189</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>46295</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44622</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>44813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>44722</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45255</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>45364</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>44788</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>45126</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>45033</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>45002</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>44788</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45905</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>45909</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>45649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>45925</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>44910</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>44902</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>45177</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45117</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44698</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>45999</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>45799</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>45217</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>46170</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>46178</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>46183</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>46189</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>46275</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>45272</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>45182</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>44802</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>45446</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>45735</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>44586</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44553</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>44523</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44579</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>44693</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44845</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44869</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44830</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44603</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>44827</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44523</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44687</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44522</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>44650</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44813</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>44694</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>44746</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>44482</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>44481</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44572</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>44529</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44813</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>44813</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44764</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>44762</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>44510</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>44510</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44575</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>44595</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>44805</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>44700</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>44553</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44516</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>44487</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>44505</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>44662</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         <v>44614</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>44623</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>44830</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>44830</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>44788</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>44806</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>44731</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>44610</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>44831</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>44788</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>44721</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>44834</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>44557</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>44843</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>44609</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>44610</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>44823</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>45255</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>45259</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>44573</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>44573</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>45390</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>45453</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>44594</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>44783</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>45573</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>45342</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>45342</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45117</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>44900</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>45589</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>45589</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>45321</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>44749</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45259</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>45371</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>45369</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>45370</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>45035</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>45119</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>45100</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>45483</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>44902</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45733</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>45217</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>45385</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>44895</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>44826</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44904</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>45360</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>45683</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>45141</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>45105</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45723</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>44823</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>44481</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>45211</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>45447</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>45353</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>45093</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>45443</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>44872</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>44804</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>44921</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>45107</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>45208</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>44557</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>44557</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>45537</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>45268</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45238</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>45240</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>45015</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>45082</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45063</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>45141</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>45273</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>45884</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>45471</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>45628</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>45648</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>44949</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>44895</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>45448</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>45110</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>45019</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>45033</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>45436</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>45446</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>44522</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>45231</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>45884</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>45154</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>45453</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>45002</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>44903</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45404</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44957</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>45589</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>45078</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>45078</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>45062</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>45208</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>45323</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44557</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44921</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45434</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45362</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>45540</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>45377</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>45686</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>45093</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>45902</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>45548</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45506</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>44511</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45404</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45905</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44529</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45908</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44610</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>45909</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45096</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45162</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>45630</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>45063</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>45911</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45911</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>45911</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>44966</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45777</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>45911</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44867</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45782</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44994</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45097</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45912</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45362</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45141</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>45175</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44902</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45656</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45162</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>45518</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>45702</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>45643</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45117</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>45721</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>45177</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>45744</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>44530</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45506</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>44904</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>45011</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>45474</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>45471</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45630</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>44881</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>44585</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45534</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45923</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45534</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45719</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>45572</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45217</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>45035</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>45708</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>45930</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>45369</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44832</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>45737</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45197</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>44644</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>45722</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>44827</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>44965</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>45356</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>44524</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>44524</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45706</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>44904</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>45708</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45071</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44740</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>44658</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>45055</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>45390</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45390</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>44610</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45568</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45553</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>45364</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>45196</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23475,7 +23475,7 @@
         <v>45937</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>45937</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>45588</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45471</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>45803</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>44585</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>45937</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>45231</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>45805</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>45524</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>44662</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>45037</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>45119</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44679</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45937</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>45453</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>45463</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>45695</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>45609</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>45148</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>45635</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44663</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>45666</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>45140</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>45369</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45715</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45035</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>45686</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>45635</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>45209</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>44602</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>45834</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>44776</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>45964</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45835</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>45194</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>45838</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>45838</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>45607</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>45518</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26430,7 +26430,7 @@
         <v>45422</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>45483</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>44997</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>45468</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26727,7 +26727,7 @@
         <v>45964</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>45642</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26873,7 +26873,7 @@
         <v>45631</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
         <v>45110</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44801</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>45642</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>45197</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>45197</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>45301</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>45015</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>45091</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>45231</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>45646</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>45826</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>44757</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>45971</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44790</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>45845</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28041,7 +28041,7 @@
         <v>45844</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28114,7 +28114,7 @@
         <v>45845</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28187,7 +28187,7 @@
         <v>45973</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>45605</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>45605</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>45314</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>45666</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28557,7 +28557,7 @@
         <v>44802</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28630,7 +28630,7 @@
         <v>45265</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28703,7 +28703,7 @@
         <v>45744</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>45630</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28849,7 +28849,7 @@
         <v>44505</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>45646</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>45733</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>45688</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>45975</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>45714</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>45237</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29375,7 +29375,7 @@
         <v>45677</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29448,7 +29448,7 @@
         <v>44832</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>45453</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>45216</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>45685</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>45555</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
         <v>45737</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44873</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>45733</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>44746</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>45982</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>45685</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>44603</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30344,7 +30344,7 @@
         <v>45147</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>45377</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30495,7 +30495,7 @@
         <v>45730</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>46100</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>46100</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>45986</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>45610</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         <v>44978</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>45503</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31011,7 +31011,7 @@
         <v>45255</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>45728</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>45537</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>45652</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>45709</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>44994</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>44911</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>45012</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31600,7 +31600,7 @@
         <v>45264</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31673,7 +31673,7 @@
         <v>44838</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>45195</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>45195</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>45520</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>44965</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44790</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45036</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>45342</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>44910</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>44585</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>44580</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>46126</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32554,7 +32554,7 @@
         <v>45996</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>45436</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>46002</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32773,7 +32773,7 @@
         <v>44916</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>44951</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32919,7 +32919,7 @@
         <v>45414</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>44951</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44742</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33138,7 +33138,7 @@
         <v>44845</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33211,7 +33211,7 @@
         <v>46133</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>46133</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>46133</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33430,7 +33430,7 @@
         <v>45573</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>45555</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33576,7 +33576,7 @@
         <v>44957</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>44631</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33727,7 +33727,7 @@
         <v>45908</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>45785</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>45988</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33946,7 +33946,7 @@
         <v>45016</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34024,7 +34024,7 @@
         <v>45666</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34097,7 +34097,7 @@
         <v>45762</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34170,7 +34170,7 @@
         <v>44620</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>44620</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>46020</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34399,7 +34399,7 @@
         <v>46020</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34472,7 +34472,7 @@
         <v>45239</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>45341</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>45436</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>44487</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>45905</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>44620</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34920,7 +34920,7 @@
         <v>45071</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34993,7 +34993,7 @@
         <v>46029</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35066,7 +35066,7 @@
         <v>46029</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35139,7 +35139,7 @@
         <v>45097</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>44711</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>45539</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>46034</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35431,7 +35431,7 @@
         <v>45282</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35504,7 +35504,7 @@
         <v>45154</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35577,7 +35577,7 @@
         <v>45632</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>45575</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>46037</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>45243</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35869,7 +35869,7 @@
         <v>45217</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35942,7 +35942,7 @@
         <v>45079</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45011</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>45237</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36166,7 +36166,7 @@
         <v>45936</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>45037</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>45546</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36385,7 +36385,7 @@
         <v>44743</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36458,7 +36458,7 @@
         <v>44935</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36531,7 +36531,7 @@
         <v>45375</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>44904</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>45036</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36750,7 +36750,7 @@
         <v>45961</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36823,7 +36823,7 @@
         <v>46150</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36901,7 +36901,7 @@
         <v>46153</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>46153</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>46071</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>46076</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37203,7 +37203,7 @@
         <v>46153</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>46153</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>46153</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>46153</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>46155</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>45915</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>46155</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>46089</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37802,7 +37802,7 @@
         <v>46089</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>46079</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>46170</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>46170</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>46175</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>46176</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38240,7 +38240,7 @@
         <v>46076</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>46176</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>46180</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>46180</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>46178</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>46180</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>46183</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>46183</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>46183</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>46189</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38990,7 +38990,7 @@
         <v>46189</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39068,7 +39068,7 @@
         <v>46189</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>46189</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>46189</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>46189</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39380,7 +39380,7 @@
         <v>46189</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>46189</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>46189</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39614,7 +39614,7 @@
         <v>46189</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39692,7 +39692,7 @@
         <v>46189</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39770,7 +39770,7 @@
         <v>46189</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>46198</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>46199</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>46200</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
         <v>46199</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40145,7 +40145,7 @@
         <v>46205</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40218,7 +40218,7 @@
         <v>46210</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40291,7 +40291,7 @@
         <v>46213</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40364,7 +40364,7 @@
         <v>46213</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>46184</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40515,7 +40515,7 @@
         <v>46266</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>46265</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>46265</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>46266</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>46265</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>46265</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
         <v>46265</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41051,7 +41051,7 @@
         <v>46265</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>46265</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41207,7 +41207,7 @@
         <v>46265</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41285,7 +41285,7 @@
         <v>46265</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41363,7 +41363,7 @@
         <v>46267</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>46268</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>46268</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>46268</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41655,7 +41655,7 @@
         <v>46268</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41728,7 +41728,7 @@
         <v>46276</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
         <v>46275</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41884,7 +41884,7 @@
         <v>46276</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>46282</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42035,7 +42035,7 @@
         <v>46282</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>46290</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>46289</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>46289</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42337,7 +42337,7 @@
         <v>46253</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>46254</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>46267</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42556,7 +42556,7 @@
         <v>46247</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42629,7 +42629,7 @@
         <v>46302</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>46302</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>46303</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>46303</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42921,7 +42921,7 @@
         <v>44656</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>44635</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>44719</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>44622</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45560</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>44938</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>45476</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>44837</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43505,7 +43505,7 @@
         <v>45264</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45400</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43651,7 +43651,7 @@
         <v>45365</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43724,7 +43724,7 @@
         <v>45272</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43797,7 +43797,7 @@
         <v>45622</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>44802</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43943,7 +43943,7 @@
         <v>44802</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>44820</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>45182</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>44806</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44235,7 +44235,7 @@
         <v>45453</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44308,7 +44308,7 @@
         <v>44952</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44381,7 +44381,7 @@
         <v>44482</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44454,7 +44454,7 @@
         <v>45124</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45350</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44600,7 +44600,7 @@
         <v>45370</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>45373</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>44802</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45005</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44892,7 +44892,7 @@
         <v>44938</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45194</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>44805</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45111,7 +45111,7 @@
         <v>44896</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>45652</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>45735</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>45737</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45939</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>45939</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45980</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>46030</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45695,7 +45695,7 @@
         <v>46049</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45768,7 +45768,7 @@
         <v>46104</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>46134</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>46134</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>

--- a/Översikt OSBY.xlsx
+++ b/Översikt OSBY.xlsx
@@ -601,7 +601,7 @@
         <v>45589</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>46134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45177</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45844</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>44802</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>44827</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>46241</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>45796</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>46030</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>46134</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>46134</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>46153</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>45356</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45078</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>45607</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>45867</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>45918</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>46153</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>46189</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>46295</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44622</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>44813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>44722</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45255</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>45364</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>44788</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>45126</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>45033</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>45002</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>44788</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45905</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>45909</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>45649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>45925</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>44910</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>44902</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>45177</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45117</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44698</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>45999</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>45799</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>45217</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>46170</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>46178</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>46183</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>46189</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>46275</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>45272</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>45182</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>44802</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>45446</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>45735</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>44586</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44553</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>44523</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44579</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>44693</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44845</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44869</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44830</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44603</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>44827</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44523</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44687</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44522</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>44650</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44813</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>44694</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>44746</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>44482</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>44481</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44572</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>44529</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44813</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>44813</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44764</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>44762</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>44510</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>44510</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44575</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>44595</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>44805</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>44700</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>44553</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44516</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>44487</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>44505</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>44662</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         <v>44614</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>44623</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>44830</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>44830</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>44788</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>44806</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>44731</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>44610</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>44831</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>44788</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>44721</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>44834</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>44557</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>44843</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>44609</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>44610</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>44823</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>45255</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>45259</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>44573</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>44573</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>45390</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>45453</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>44594</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>44783</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>45573</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>45342</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>45342</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45117</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>44900</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>45589</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>45589</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>45321</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>44749</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45259</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>45371</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>45369</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>45370</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>45035</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>45119</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>45100</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>45483</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>44902</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45733</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>45217</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>45385</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>44895</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>44826</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44904</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>45360</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>45683</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>45141</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>45105</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45723</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>44823</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>44481</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>45211</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>45447</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>45353</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>45093</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>45443</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>44872</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>44804</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>44921</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>45107</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>45208</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>44557</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>44557</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>45537</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>45268</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45238</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>45240</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>45015</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>45082</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45063</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>45141</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>45273</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>45884</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>45471</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>45628</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>45648</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>44949</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>44895</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>45448</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>45110</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>45019</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>45033</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>45436</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>45446</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>44522</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>45231</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>45884</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>45154</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>45453</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>45002</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>44903</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45404</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44957</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>45589</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>45078</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>45078</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>45062</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>45208</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>45323</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44557</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44921</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45434</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45362</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>45540</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>45377</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>45686</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>45093</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>45902</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>45548</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45506</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>44511</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45404</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45905</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44529</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45908</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44610</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>45909</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45096</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45162</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>45630</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>45063</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>45911</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45911</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>45911</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>44966</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45777</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>45911</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44867</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45782</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44994</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45097</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45912</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45362</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45141</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>45175</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>44902</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45656</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45162</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>45518</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>45702</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>45643</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45117</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>45721</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>45177</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>45744</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>44530</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45506</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>44904</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>45011</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>45474</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>45471</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45630</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>44881</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>44585</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45534</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45923</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45534</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45719</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>45572</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45217</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>45035</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>45708</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>45930</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>45369</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44832</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>45737</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45197</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>44644</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>45722</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>44827</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>44965</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>45356</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>44524</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>44524</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45706</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>44904</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>45708</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45071</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>44740</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>44658</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>45055</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>45390</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45390</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>44610</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45568</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45553</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>45364</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>45196</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23475,7 +23475,7 @@
         <v>45937</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>45937</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>45588</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45471</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>45803</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>44585</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>45937</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>45231</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>45805</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>45524</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>44662</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>45037</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>45119</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44679</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45937</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>45453</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>45463</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>45695</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>45609</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>45148</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>45635</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44663</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>45666</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>45140</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>45369</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45715</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45035</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>45686</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>45635</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>45209</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>44602</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>45834</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>44776</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>45964</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45835</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>45194</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>45838</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>45838</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>45607</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>45518</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26430,7 +26430,7 @@
         <v>45422</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>45483</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>44997</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>45468</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26727,7 +26727,7 @@
         <v>45964</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>45642</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26873,7 +26873,7 @@
         <v>45631</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
         <v>45110</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44801</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>45642</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>45197</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>45197</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>45301</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>45015</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>45091</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>45231</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>45646</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>45826</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>44757</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>45971</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44790</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>45845</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28041,7 +28041,7 @@
         <v>45844</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28114,7 +28114,7 @@
         <v>45845</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28187,7 +28187,7 @@
         <v>45973</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>45605</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>45605</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>45314</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>45666</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28557,7 +28557,7 @@
         <v>44802</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28630,7 +28630,7 @@
         <v>45265</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28703,7 +28703,7 @@
         <v>45744</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>45630</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28849,7 +28849,7 @@
         <v>44505</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>45646</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>45733</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>45688</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>45975</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>45714</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>45237</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29375,7 +29375,7 @@
         <v>45677</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29448,7 +29448,7 @@
         <v>44832</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>45453</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>45216</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>45685</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>45555</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
         <v>45737</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44873</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>45733</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>44746</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>45982</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>45685</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>44603</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30344,7 +30344,7 @@
         <v>45147</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>45377</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30495,7 +30495,7 @@
         <v>45730</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>46100</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>46100</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>45986</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>45610</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         <v>44978</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>45503</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31011,7 +31011,7 @@
         <v>45255</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>45728</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>45537</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>45652</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>45709</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>44994</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>44911</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>45012</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31600,7 +31600,7 @@
         <v>45264</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31673,7 +31673,7 @@
         <v>44838</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>45195</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>45195</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>45520</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>44965</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44790</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45036</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>45342</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>44910</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>44585</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>44580</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>46126</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32554,7 +32554,7 @@
         <v>45996</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>45436</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>46002</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32773,7 +32773,7 @@
         <v>44916</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>44951</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32919,7 +32919,7 @@
         <v>45414</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>44951</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44742</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33138,7 +33138,7 @@
         <v>44845</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33211,7 +33211,7 @@
         <v>46133</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>46133</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>46133</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33430,7 +33430,7 @@
         <v>45573</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>45555</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33576,7 +33576,7 @@
         <v>44957</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>44631</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33727,7 +33727,7 @@
         <v>45908</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>45785</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>45988</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33946,7 +33946,7 @@
         <v>45016</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34024,7 +34024,7 @@
         <v>45666</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34097,7 +34097,7 @@
         <v>45762</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34170,7 +34170,7 @@
         <v>44620</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>44620</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>46020</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34399,7 +34399,7 @@
         <v>46020</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34472,7 +34472,7 @@
         <v>45239</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>45341</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>45436</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>44487</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>45905</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>44620</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34920,7 +34920,7 @@
         <v>45071</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34993,7 +34993,7 @@
         <v>46029</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35066,7 +35066,7 @@
         <v>46029</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35139,7 +35139,7 @@
         <v>45097</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>44711</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>45539</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>46034</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35431,7 +35431,7 @@
         <v>45282</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35504,7 +35504,7 @@
         <v>45154</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35577,7 +35577,7 @@
         <v>45632</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>45575</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>46037</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>45243</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35869,7 +35869,7 @@
         <v>45217</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35942,7 +35942,7 @@
         <v>45079</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45011</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>45237</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36166,7 +36166,7 @@
         <v>45936</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>45037</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>45546</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36385,7 +36385,7 @@
         <v>44743</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36458,7 +36458,7 @@
         <v>44935</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36531,7 +36531,7 @@
         <v>45375</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>44904</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>45036</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36750,7 +36750,7 @@
         <v>45961</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36823,7 +36823,7 @@
         <v>46150</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36901,7 +36901,7 @@
         <v>46153</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>46153</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>46071</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>46076</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37203,7 +37203,7 @@
         <v>46153</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>46153</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>46153</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>46153</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>46155</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>45915</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>46155</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>46089</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37802,7 +37802,7 @@
         <v>46089</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>46079</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>46170</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>46170</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>46175</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>46176</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38240,7 +38240,7 @@
         <v>46076</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>46176</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>46180</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>46180</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>46178</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>46180</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>46183</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>46183</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>46183</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>46189</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38990,7 +38990,7 @@
         <v>46189</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39068,7 +39068,7 @@
         <v>46189</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>46189</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>46189</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>46189</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39380,7 +39380,7 @@
         <v>46189</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>46189</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>46189</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39614,7 +39614,7 @@
         <v>46189</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39692,7 +39692,7 @@
         <v>46189</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39770,7 +39770,7 @@
         <v>46189</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>46198</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>46199</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>46200</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
         <v>46199</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40145,7 +40145,7 @@
         <v>46205</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40218,7 +40218,7 @@
         <v>46210</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40291,7 +40291,7 @@
         <v>46213</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40364,7 +40364,7 @@
         <v>46213</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>46184</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40515,7 +40515,7 @@
         <v>46266</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40588,7 +40588,7 @@
         <v>46265</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>46265</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>46266</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>46265</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>46265</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
         <v>46265</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41051,7 +41051,7 @@
         <v>46265</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>46265</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41207,7 +41207,7 @@
         <v>46265</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41285,7 +41285,7 @@
         <v>46265</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41363,7 +41363,7 @@
         <v>46267</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>46268</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>46268</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>46268</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41655,7 +41655,7 @@
         <v>46268</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41728,7 +41728,7 @@
         <v>46276</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
         <v>46275</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41884,7 +41884,7 @@
         <v>46276</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>46282</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42035,7 +42035,7 @@
         <v>46282</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>46290</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>46289</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>46289</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42337,7 +42337,7 @@
         <v>46253</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>46254</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>46267</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42556,7 +42556,7 @@
         <v>46247</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42629,7 +42629,7 @@
         <v>46302</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>46302</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>46303</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>46303</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42921,7 +42921,7 @@
         <v>44656</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>44635</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>44719</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>44622</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45560</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>44938</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>45476</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>44837</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43505,7 +43505,7 @@
         <v>45264</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45400</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43651,7 +43651,7 @@
         <v>45365</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43724,7 +43724,7 @@
         <v>45272</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43797,7 +43797,7 @@
         <v>45622</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>44802</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43943,7 +43943,7 @@
         <v>44802</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>44820</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>45182</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>44806</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44235,7 +44235,7 @@
         <v>45453</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44308,7 +44308,7 @@
         <v>44952</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44381,7 +44381,7 @@
         <v>44482</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44454,7 +44454,7 @@
         <v>45124</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45350</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44600,7 +44600,7 @@
         <v>45370</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>45373</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>44802</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45005</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44892,7 +44892,7 @@
         <v>44938</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45194</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>44805</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45111,7 +45111,7 @@
         <v>44896</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>45652</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>45735</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>45737</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>45939</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>45939</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45980</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>46030</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45695,7 +45695,7 @@
         <v>46049</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45768,7 +45768,7 @@
         <v>46104</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>46134</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>46134</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>

--- a/Översikt OSBY.xlsx
+++ b/Översikt OSBY.xlsx
@@ -601,7 +601,7 @@
         <v>45589</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>46134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45177</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45844</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>44802</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>44827</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>46241</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>45796</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>46030</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>46134</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>46134</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>46153</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>46153</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45918</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>46189</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>45078</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45607</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>46295</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>45356</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>45867</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44622</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>44813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>44722</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>44788</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>45117</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>45177</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>45033</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>45217</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45799</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>45905</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>45909</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>45925</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>45999</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>46170</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>46178</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>46183</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>46189</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>45002</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>45364</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>46275</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>45126</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>44698</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>45255</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44910</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>45649</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>44902</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>45272</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>45182</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>44802</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>45446</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>45735</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>44586</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44553</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>44579</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44523</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>44693</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44845</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44869</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44830</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44603</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>44827</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44522</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44687</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44523</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>44650</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44813</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>44694</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>44746</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>44572</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>44813</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>44813</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>44529</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>44764</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>44762</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44510</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>44510</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>44575</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>44595</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>44487</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>44505</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>44806</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>44731</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44610</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>44557</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>44609</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>44843</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>44700</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>44662</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         <v>44830</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>44830</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>44831</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>44823</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>44553</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>44614</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>44788</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>44805</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>44623</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>44788</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>44721</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>44834</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>44610</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>44573</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>44573</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>45447</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>45453</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>45369</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>45607</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44965</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>44881</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>44900</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>45078</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>45063</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>45196</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>44895</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44994</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>45259</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>45709</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>45035</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>45037</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>45268</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>45666</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>45238</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45015</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>45097</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44790</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>45643</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>45573</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>45231</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45231</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>45652</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>45353</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>45728</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>44740</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>45506</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44904</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>44904</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>45605</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>45605</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>45211</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>44594</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>45646</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>44585</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>45733</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>45555</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>45209</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44662</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>44904</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>45631</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>45019</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45362</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>45722</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
         <v>44921</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>44585</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>45568</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>45548</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>45683</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>44903</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>45685</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>44832</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>45609</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>45062</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>44585</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>45110</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>45471</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>44826</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>44602</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45082</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>45537</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>44580</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>45243</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44742</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>45093</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45036</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>45730</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>45240</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>44916</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>44801</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45468</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>45483</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>44749</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45463</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>45015</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>45404</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>44867</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>44663</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>45656</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>45273</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>45666</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45033</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>45037</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>44743</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>45107</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>44529</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44746</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>45524</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>45762</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45154</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>45539</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>44832</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>44783</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45884</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45162</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>45785</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>44511</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44978</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>44620</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44757</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45323</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>44951</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45369</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>45666</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45175</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45642</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>45390</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>45884</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>45100</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45141</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>44644</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>45936</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45575</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45902</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45342</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>45436</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>45695</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>45905</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45632</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>45908</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>45534</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45534</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>45909</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45141</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45911</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45911</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>45911</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45911</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>44845</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45912</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>45677</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44711</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44524</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>44524</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>45961</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>45923</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45930</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>44776</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>46153</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>46150</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>46153</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>46153</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>45282</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>46153</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45937</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>44790</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21587,7 +21587,7 @@
         <v>45937</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21665,7 +21665,7 @@
         <v>45937</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45937</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>45589</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>45589</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>45686</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>44904</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>46153</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>45011</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>45414</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>46155</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>45506</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>45091</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>44902</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>46153</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>45434</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>45648</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>45119</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>45915</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>44838</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>46155</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23140,7 +23140,7 @@
         <v>46079</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>45589</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>45964</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>45964</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>45197</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>45610</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23578,7 +23578,7 @@
         <v>45737</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>45973</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>45971</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>45012</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>44658</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>45975</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>45369</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>45982</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>45733</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>45237</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>45986</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45360</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>45148</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>44557</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45404</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45154</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>45520</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>44911</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45208</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>45996</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>45436</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>45706</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>46170</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>46170</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>45630</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>46002</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44610</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45443</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>45036</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>45503</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>45448</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>45714</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>46020</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>46020</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>45905</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44997</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>45259</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>46029</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>46029</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>45119</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>45208</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>45377</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>46034</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>46176</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>46175</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>46176</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>46178</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>46180</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>46180</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>46037</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>46180</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>46076</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>45239</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45321</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>45646</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>44994</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>45371</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45231</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>44965</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>45264</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45364</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>46183</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>46183</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>45197</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28295,7 +28295,7 @@
         <v>45197</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>45096</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>46183</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         <v>45540</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>45162</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>46071</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28738,7 +28738,7 @@
         <v>44895</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>45446</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28884,7 +28884,7 @@
         <v>46076</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>44910</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>44951</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>46189</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>46189</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>46189</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>46189</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29420,7 +29420,7 @@
         <v>46189</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>46189</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>46089</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>46189</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>46189</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>46089</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>44873</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>46189</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>46189</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>46189</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>46189</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>45063</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>44557</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30409,7 +30409,7 @@
         <v>45436</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>46100</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>46100</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>45635</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>45079</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45002</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>45097</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>45301</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>45078</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>46198</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>44921</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>46199</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>45110</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>46200</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>46126</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>46199</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>44802</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>45140</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>45733</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>45390</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>44505</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>46133</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>45744</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>46133</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>46133</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>45147</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>44935</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>45216</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>44522</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>44620</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32619,7 +32619,7 @@
         <v>45195</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>45195</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>45375</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>44620</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>45572</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>45908</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33062,7 +33062,7 @@
         <v>45988</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>46205</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>46210</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45390</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>45588</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33432,7 +33432,7 @@
         <v>45117</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>45573</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>46213</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>46184</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33734,7 +33734,7 @@
         <v>46213</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33807,7 +33807,7 @@
         <v>45016</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         <v>44631</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>45341</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>45362</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>44966</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>45177</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>45377</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>45642</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>45555</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>45453</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>45471</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>46275</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45217</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34776,7 +34776,7 @@
         <v>45686</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>46276</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34927,7 +34927,7 @@
         <v>45370</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>45628</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>46276</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44557</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>45194</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>45035</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>45237</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
         <v>44872</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35521,7 +35521,7 @@
         <v>45071</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35594,7 +35594,7 @@
         <v>45217</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35667,7 +35667,7 @@
         <v>44487</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>44949</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44957</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35886,7 +35886,7 @@
         <v>46282</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>45715</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>46282</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>45688</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>45141</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36251,7 +36251,7 @@
         <v>45093</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>45546</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>44603</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45723</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>44823</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36616,7 +36616,7 @@
         <v>45630</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36689,7 +36689,7 @@
         <v>44610</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>44530</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>46289</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36913,7 +36913,7 @@
         <v>45483</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36991,7 +36991,7 @@
         <v>45255</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37064,7 +37064,7 @@
         <v>45117</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37137,7 +37137,7 @@
         <v>45537</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>44804</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37283,7 +37283,7 @@
         <v>45342</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>45342</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>46289</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37507,7 +37507,7 @@
         <v>45011</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37580,7 +37580,7 @@
         <v>45071</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>45422</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37726,7 +37726,7 @@
         <v>46290</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>44679</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>45685</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>45105</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>45314</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45385</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>45255</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38247,7 +38247,7 @@
         <v>45217</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38325,7 +38325,7 @@
         <v>44902</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38403,7 +38403,7 @@
         <v>44957</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         <v>45265</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38549,7 +38549,7 @@
         <v>46254</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38622,7 +38622,7 @@
         <v>46253</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>46247</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38768,7 +38768,7 @@
         <v>45453</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38841,7 +38841,7 @@
         <v>45035</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>45777</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>45782</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>45630</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39133,7 +39133,7 @@
         <v>45518</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39211,7 +39211,7 @@
         <v>46303</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>46302</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>45702</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45721</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>45474</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>46302</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>45719</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>46265</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39800,7 +39800,7 @@
         <v>44827</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39873,7 +39873,7 @@
         <v>46303</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>45708</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>45737</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>45356</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>45803</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>45471</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>45553</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>46266</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45708</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40535,7 +40535,7 @@
         <v>46265</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40613,7 +40613,7 @@
         <v>46265</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40691,7 +40691,7 @@
         <v>45055</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>46308</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40842,7 +40842,7 @@
         <v>46266</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40915,7 +40915,7 @@
         <v>45805</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>46265</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>46265</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41144,7 +41144,7 @@
         <v>46265</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41222,7 +41222,7 @@
         <v>46265</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41300,7 +41300,7 @@
         <v>46265</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>46265</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>46309</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>46268</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>46267</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>46268</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>46268</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>46267</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>45635</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>46310</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>45834</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>45835</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>45518</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42264,7 +42264,7 @@
         <v>45838</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42337,7 +42337,7 @@
         <v>45838</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45826</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45845</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42556,7 +42556,7 @@
         <v>45845</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42629,7 +42629,7 @@
         <v>45844</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>45744</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45453</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42853,7 +42853,7 @@
         <v>45560</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42926,7 +42926,7 @@
         <v>44938</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
         <v>44656</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43072,7 +43072,7 @@
         <v>45476</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>44837</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45264</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>45400</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>45365</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>45272</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>45622</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>44802</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>44802</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>44820</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>45182</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>44806</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45453</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>44952</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45124</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>45350</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>45370</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45373</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44386,7 +44386,7 @@
         <v>44802</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>44635</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44532,7 +44532,7 @@
         <v>45005</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>44719</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>44938</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45194</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44824,7 +44824,7 @@
         <v>44805</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44897,7 +44897,7 @@
         <v>44896</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44970,7 +44970,7 @@
         <v>44622</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45043,7 +45043,7 @@
         <v>45652</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>45735</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45737</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>45939</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45335,7 +45335,7 @@
         <v>45939</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>45980</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45481,7 +45481,7 @@
         <v>46030</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>46049</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45627,7 +45627,7 @@
         <v>46104</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45700,7 +45700,7 @@
         <v>46134</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45773,7 +45773,7 @@
         <v>46134</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>

--- a/Översikt OSBY.xlsx
+++ b/Översikt OSBY.xlsx
@@ -601,7 +601,7 @@
         <v>45589</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>46134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45177</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45844</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>44802</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>44827</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>46241</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>45796</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>46030</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>46134</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>46134</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>46153</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>46153</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45918</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>46189</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>45078</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45607</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>46295</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>45356</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>45867</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44622</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>44813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>44722</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>44788</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>45117</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>45177</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>45033</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>45217</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45799</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>45905</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>45909</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>45925</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>44788</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>45999</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>46170</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>46178</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>46183</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>46189</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>45002</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>45364</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>46275</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>45126</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>44698</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>45255</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44910</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>45649</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>44902</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>45272</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>45182</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>44802</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>45446</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>45735</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>44586</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44553</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>44579</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44523</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>44693</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44845</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44869</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44830</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44603</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>44827</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44522</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44687</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44523</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>44650</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44813</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>44694</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>44746</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>44572</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>44813</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>44813</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>44529</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>44764</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>44762</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44510</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>44510</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>44575</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>44595</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>44487</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>44505</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>44806</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>44731</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44610</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>44557</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>44609</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>44843</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>44700</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>44662</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         <v>44830</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>44830</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>44831</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>44823</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>44553</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>44614</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>44788</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>44805</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>44623</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>44788</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>44721</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>44834</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>44610</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>44573</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>44573</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>45447</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>45453</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>45369</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>45607</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44965</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>44881</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>44900</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>45078</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>45063</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>45196</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>44895</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44994</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>45259</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>45709</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>45035</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>45037</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>45268</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>45666</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>45238</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45015</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>45097</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44790</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>45643</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>45573</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>45231</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45231</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>45652</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>45353</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>45728</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>44740</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>45506</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44904</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>44904</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>45605</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>45605</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>45211</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>44594</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>45646</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>44585</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>45733</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>45555</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>45209</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44662</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>44904</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>45631</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>45019</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45362</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>45722</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
         <v>44921</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>44585</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>45568</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>45548</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>45683</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>44903</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>45685</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>44832</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>45609</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>45062</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>44585</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>45110</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>45471</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>44826</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>44602</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45082</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>45537</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>44580</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>45243</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44742</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>45093</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45036</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>45730</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>45240</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>44916</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>44801</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45468</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>45483</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>44749</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45463</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>45015</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>45404</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>44867</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>44663</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>45656</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>45273</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>45666</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45033</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>45037</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>44743</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>45107</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>44529</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44746</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>45524</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>45762</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45154</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>45539</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>44832</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>44783</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45884</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45162</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>45785</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>44511</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44978</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>44620</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44757</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45323</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>44951</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45369</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>45666</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45175</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45642</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>45390</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>45884</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>45100</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45141</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>44644</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>45936</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45575</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45902</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45342</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>45436</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>45695</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>45905</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45632</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>45908</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>45534</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45534</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>45909</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45141</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45911</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45911</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>45911</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45911</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>44845</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45912</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>45677</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44711</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44524</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>44524</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>45961</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>45923</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45930</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>44776</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>46153</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>46150</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>46153</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>46153</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>45282</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>46153</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45937</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>44790</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21587,7 +21587,7 @@
         <v>45937</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21665,7 +21665,7 @@
         <v>45937</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45937</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>45589</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>45589</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>45686</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>44904</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>46153</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>45011</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>45414</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>46155</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>45506</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>45091</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>44902</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>46153</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>45434</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>45648</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>45119</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>45915</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>44838</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>46155</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23140,7 +23140,7 @@
         <v>46079</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>45589</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>45964</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>45964</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>45197</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>45610</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23578,7 +23578,7 @@
         <v>45737</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>45973</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>45971</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>45012</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>44658</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>45975</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>45369</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>45982</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>45733</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>45237</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>45986</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45360</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>45148</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>44557</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45404</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45154</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>45520</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>44911</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45208</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>45996</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>45436</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>45706</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>46170</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>46170</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>45630</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>46002</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44610</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45443</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>45036</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>45503</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>45448</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>45714</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>46020</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>46020</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>45905</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44997</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>45259</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>46029</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>46029</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>45119</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>45208</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>45377</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>46034</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>46176</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>46175</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>46176</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>46178</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>46180</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>46180</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>46037</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>46180</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>46076</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>45239</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45321</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>45646</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>44994</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>45371</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45231</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>44965</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>45264</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45364</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>46183</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>46183</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>45197</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28295,7 +28295,7 @@
         <v>45197</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>45096</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>46183</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         <v>45540</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>45162</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>46071</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28738,7 +28738,7 @@
         <v>44895</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>45446</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28884,7 +28884,7 @@
         <v>46076</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>44910</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>44951</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>46189</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>46189</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>46189</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>46189</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29420,7 +29420,7 @@
         <v>46189</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>46189</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>46089</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>46189</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>46189</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>46089</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>44873</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>46189</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>46189</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>46189</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>46189</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>45063</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>44557</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30409,7 +30409,7 @@
         <v>45436</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>46100</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>46100</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>45635</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>45079</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45002</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>45097</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>45301</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>45078</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>46198</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>44921</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>46199</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>45110</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>46200</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>46126</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>46199</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>44802</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>45140</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>45733</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>45390</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>44505</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>46133</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>45744</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>46133</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>46133</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>45147</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>44935</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>45216</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>44522</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>44620</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32619,7 +32619,7 @@
         <v>45195</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>45195</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>45375</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>44620</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>45572</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>45908</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33062,7 +33062,7 @@
         <v>45988</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>46205</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>46210</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>45390</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>45588</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33432,7 +33432,7 @@
         <v>45117</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>45573</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>46213</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>46184</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33734,7 +33734,7 @@
         <v>46213</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33807,7 +33807,7 @@
         <v>45016</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         <v>44631</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>45341</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>45362</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>44966</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>45177</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>45377</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>45642</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>45555</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>45453</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>45471</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>46275</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45217</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34776,7 +34776,7 @@
         <v>45686</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>46276</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34927,7 +34927,7 @@
         <v>45370</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>45628</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>46276</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44557</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>45194</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>45035</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>45237</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
         <v>44872</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35521,7 +35521,7 @@
         <v>45071</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35594,7 +35594,7 @@
         <v>45217</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35667,7 +35667,7 @@
         <v>44487</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>44949</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44957</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35886,7 +35886,7 @@
         <v>46282</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>45715</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>46282</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>45688</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>45141</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36251,7 +36251,7 @@
         <v>45093</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>45546</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>44603</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45723</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>44823</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36616,7 +36616,7 @@
         <v>45630</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36689,7 +36689,7 @@
         <v>44610</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>44530</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>46289</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36913,7 +36913,7 @@
         <v>45483</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36991,7 +36991,7 @@
         <v>45255</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37064,7 +37064,7 @@
         <v>45117</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37137,7 +37137,7 @@
         <v>45537</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>44804</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37283,7 +37283,7 @@
         <v>45342</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>45342</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>46289</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37507,7 +37507,7 @@
         <v>45011</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37580,7 +37580,7 @@
         <v>45071</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>45422</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37726,7 +37726,7 @@
         <v>46290</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>44679</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>45685</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>45105</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>45314</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45385</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>45255</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38247,7 +38247,7 @@
         <v>45217</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38325,7 +38325,7 @@
         <v>44902</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38403,7 +38403,7 @@
         <v>44957</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         <v>45265</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38549,7 +38549,7 @@
         <v>46254</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38622,7 +38622,7 @@
         <v>46253</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>46247</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38768,7 +38768,7 @@
         <v>45453</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38841,7 +38841,7 @@
         <v>45035</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>45777</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>45782</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>45630</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39133,7 +39133,7 @@
         <v>45518</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39211,7 +39211,7 @@
         <v>46303</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>46302</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>45702</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45721</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>45474</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>46302</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>45719</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>46265</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39800,7 +39800,7 @@
         <v>44827</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39873,7 +39873,7 @@
         <v>46303</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>45708</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>45737</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>45356</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>45803</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>45471</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>45553</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>46266</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45708</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40535,7 +40535,7 @@
         <v>46265</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40613,7 +40613,7 @@
         <v>46265</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40691,7 +40691,7 @@
         <v>45055</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>46308</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40842,7 +40842,7 @@
         <v>46266</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40915,7 +40915,7 @@
         <v>45805</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>46265</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>46265</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41144,7 +41144,7 @@
         <v>46265</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41222,7 +41222,7 @@
         <v>46265</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41300,7 +41300,7 @@
         <v>46265</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>46265</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>46309</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>46268</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>46267</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>46268</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>46268</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>46267</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>45635</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>46310</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>45834</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>45835</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>45518</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42264,7 +42264,7 @@
         <v>45838</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42337,7 +42337,7 @@
         <v>45838</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45826</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45845</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42556,7 +42556,7 @@
         <v>45845</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42629,7 +42629,7 @@
         <v>45844</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>45744</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45453</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42853,7 +42853,7 @@
         <v>45560</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42926,7 +42926,7 @@
         <v>44938</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
         <v>44656</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43072,7 +43072,7 @@
         <v>45476</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>44837</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45264</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>45400</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>45365</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>45272</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>45622</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>44802</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>44802</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>44820</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>45182</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>44806</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45453</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>44952</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45124</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>45350</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>45370</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45373</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44386,7 +44386,7 @@
         <v>44802</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>44635</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44532,7 +44532,7 @@
         <v>45005</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>44719</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>44938</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45194</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44824,7 +44824,7 @@
         <v>44805</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44897,7 +44897,7 @@
         <v>44896</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44970,7 +44970,7 @@
         <v>44622</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45043,7 +45043,7 @@
         <v>45652</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>45735</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45737</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>45939</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45335,7 +45335,7 @@
         <v>45939</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>45980</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45481,7 +45481,7 @@
         <v>46030</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>46049</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45627,7 +45627,7 @@
         <v>46104</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45700,7 +45700,7 @@
         <v>46134</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45773,7 +45773,7 @@
         <v>46134</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>

--- a/Översikt OSBY.xlsx
+++ b/Översikt OSBY.xlsx
@@ -601,7 +601,7 @@
         <v>45589</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>46134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45177</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45844</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>44802</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>46318</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>44827</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>46241</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>45796</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>46030</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>46134</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>46134</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>46153</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>46189</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>45356</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>46295</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>45918</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>45867</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>46153</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>45078</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>45607</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>44622</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>44813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>44852</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>44722</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>44788</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>45905</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>45909</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>45364</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45925</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>46170</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>46178</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>46183</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>46189</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>45033</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>45999</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>45649</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>44902</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45799</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45217</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>46275</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>44910</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>45255</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45126</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>45002</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>44788</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>45177</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>45117</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>44698</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>45272</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>45182</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45446</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>45735</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         <v>44586</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44553</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>44523</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>44579</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>44693</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>44845</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44869</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>44830</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>44603</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>44827</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>44523</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>44522</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>44687</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>44650</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>44813</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>44694</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>44746</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>44572</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>44813</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>44813</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>44529</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>44764</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>44762</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44510</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>44510</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>44575</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>44595</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>44516</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>44505</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>44806</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>44731</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>44610</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>44557</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>44843</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>44609</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>44700</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>44662</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>44830</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>44830</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>44831</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>44823</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>44553</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>44614</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>44788</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>44805</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>44623</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>44788</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>44721</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>44834</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>44610</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>44573</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>44573</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45884</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>45573</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>45483</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>45555</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>44957</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>44631</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>45884</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>45208</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>45016</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>45902</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>45390</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>45239</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>45341</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>45905</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>45436</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>45908</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>45071</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>45342</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>45342</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
         <v>45909</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>46079</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>45911</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>45911</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>45911</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12345,7 +12345,7 @@
         <v>45911</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>45097</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>44711</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>45912</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>45282</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>45632</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12783,7 +12783,7 @@
         <v>45923</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>45321</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>45243</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>45217</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>45079</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>45011</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>45237</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>45371</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>45369</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>45035</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>46170</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>45930</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>45037</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>46170</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>45546</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>44743</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>46175</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45375</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45937</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>45937</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>44904</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>45937</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>45036</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>45937</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>45453</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>44594</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>44783</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>45573</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>45217</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>45385</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>45589</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>45589</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>44823</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>46176</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>45370</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>45119</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45447</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>46076</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45093</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>46176</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44804</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>46180</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>46180</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>44557</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>44557</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>46178</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         <v>46180</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>46183</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>44904</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>45683</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>46183</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>45141</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>45105</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>46183</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45353</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>45443</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45964</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>45268</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>46189</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>46189</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>46189</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>46189</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
         <v>46189</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>46189</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17525,7 +17525,7 @@
         <v>46189</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>46189</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>46189</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>46189</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>46189</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>46189</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45964</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45537</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45971</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>45063</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>45273</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45973</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>46198</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>45628</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>46199</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>45975</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>45648</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>46200</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>46199</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         <v>45033</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>45231</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>45154</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>45453</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>45982</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>44903</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>46205</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>44957</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>45062</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45986</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45208</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45323</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>45362</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>45540</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>45686</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>45520</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>46210</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>45093</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>46213</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45471</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>46213</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>45506</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>46184</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45996</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45404</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>46002</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45777</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45782</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45518</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45702</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>45721</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>44949</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>45474</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>45630</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>46020</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>46020</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>44895</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>45905</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>46029</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>46029</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>46282</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>46282</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>45719</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45448</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>46034</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45019</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>45708</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>46037</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45737</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>45436</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44827</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45356</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>45708</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>45055</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45553</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>45446</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>45471</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>45803</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>46290</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44522</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>45805</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>46289</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23518,7 +23518,7 @@
         <v>46289</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>45635</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         <v>46071</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>46253</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>46076</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45834</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>46254</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>45835</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>46089</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>45838</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>46089</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45838</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>45518</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45826</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>44921</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>46247</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>46100</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>46100</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45845</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45844</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45845</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>46302</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>45434</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>45377</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>46302</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45744</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>45548</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>46303</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>46303</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45453</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>46126</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>46265</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>46265</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>46265</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>46265</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>44610</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>46133</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>46133</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>46133</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26400,7 +26400,7 @@
         <v>46265</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>45162</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>46265</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>44994</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45097</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45362</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>46265</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>44902</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>46265</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27087,7 +27087,7 @@
         <v>45908</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>45785</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27233,7 +27233,7 @@
         <v>45988</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         <v>46310</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27379,7 +27379,7 @@
         <v>46308</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>45666</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>45762</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>45177</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44620</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>46266</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>44620</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>45744</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>44530</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>46267</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45506</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>46266</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>46309</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>44904</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>46267</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>44620</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>46268</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28645,7 +28645,7 @@
         <v>46268</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28718,7 +28718,7 @@
         <v>44881</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>46314</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>45539</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28937,7 +28937,7 @@
         <v>46265</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>45154</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
         <v>45572</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>46268</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>46314</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>46310</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>45575</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>45936</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29531,7 +29531,7 @@
         <v>45369</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>45197</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29677,7 +29677,7 @@
         <v>44935</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>45722</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
         <v>46275</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44965</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>46276</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>44524</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>44524</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>46276</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44904</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>45071</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>44740</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30495,7 +30495,7 @@
         <v>45390</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>45390</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30651,7 +30651,7 @@
         <v>44610</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>45568</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>45364</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
         <v>45588</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45231</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>45961</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>46150</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45524</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>44662</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>45037</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>44679</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>46153</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>46153</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>46153</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>46153</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>45463</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>46153</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>46153</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31995,7 +31995,7 @@
         <v>46155</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32068,7 +32068,7 @@
         <v>45915</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>46155</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>45369</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>45035</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32360,7 +32360,7 @@
         <v>45635</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>44602</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>45607</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32584,7 +32584,7 @@
         <v>45483</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32662,7 +32662,7 @@
         <v>44997</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>45468</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45642</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>44801</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>45642</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45015</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>45091</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>45646</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>44757</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>45605</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>45605</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>45666</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>45630</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>44505</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45646</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45733</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>45688</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>45714</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>45677</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>44832</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45685</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45737</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>44746</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>45685</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>45377</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34517,7 +34517,7 @@
         <v>45730</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>45503</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34663,7 +34663,7 @@
         <v>45255</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34736,7 +34736,7 @@
         <v>45728</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45537</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>45709</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>44994</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>45012</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>45264</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>44838</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>45195</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>45195</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>44965</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>44790</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>45036</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>44910</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45255</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>45259</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>45117</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44900</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>44749</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>45259</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>44902</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>45733</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>44895</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>44826</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>45360</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36498,7 +36498,7 @@
         <v>45723</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>45211</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44872</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>44921</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>45107</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45238</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45240</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>45015</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>45082</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37165,7 +37165,7 @@
         <v>45141</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>45110</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>45002</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37384,7 +37384,7 @@
         <v>45404</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37457,7 +37457,7 @@
         <v>45589</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>45078</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37603,7 +37603,7 @@
         <v>45078</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37676,7 +37676,7 @@
         <v>44557</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>44511</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>44529</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>45096</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37973,7 +37973,7 @@
         <v>45630</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>45063</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>44966</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>44867</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>45141</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>45175</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38411,7 +38411,7 @@
         <v>45656</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>45162</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45643</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38630,7 +38630,7 @@
         <v>45117</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38708,7 +38708,7 @@
         <v>45011</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38781,7 +38781,7 @@
         <v>45471</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>44585</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45534</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45534</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>45217</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39156,7 +39156,7 @@
         <v>45035</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>44832</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>44644</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>45706</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>44658</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>45196</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>44585</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>45119</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>45453</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>45695</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45609</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39964,7 +39964,7 @@
         <v>45148</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>44663</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>45666</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45140</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>45715</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>45686</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>45209</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>44776</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>45194</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>45422</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40694,7 +40694,7 @@
         <v>45631</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>45110</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>45197</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40913,7 +40913,7 @@
         <v>45197</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40986,7 +40986,7 @@
         <v>45301</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41059,7 +41059,7 @@
         <v>45231</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>44790</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41205,7 +41205,7 @@
         <v>45314</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>44802</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>45265</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45237</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41497,7 +41497,7 @@
         <v>45216</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>45555</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>44873</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41716,7 +41716,7 @@
         <v>45733</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>44603</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41867,7 +41867,7 @@
         <v>45147</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>45610</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>44978</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>45652</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>44911</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>45342</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42310,7 +42310,7 @@
         <v>44585</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42383,7 +42383,7 @@
         <v>44580</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>45436</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
         <v>44916</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>44951</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>45414</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>44951</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42821,7 +42821,7 @@
         <v>44742</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>44845</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42967,7 +42967,7 @@
         <v>44656</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>44635</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43113,7 +43113,7 @@
         <v>44719</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43186,7 +43186,7 @@
         <v>44622</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45560</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>44938</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>45476</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43478,7 +43478,7 @@
         <v>44837</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43551,7 +43551,7 @@
         <v>45264</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43624,7 +43624,7 @@
         <v>45400</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43697,7 +43697,7 @@
         <v>45365</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43770,7 +43770,7 @@
         <v>45272</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45622</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44802</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43989,7 +43989,7 @@
         <v>44802</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>44820</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44135,7 +44135,7 @@
         <v>45182</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44208,7 +44208,7 @@
         <v>44806</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44281,7 +44281,7 @@
         <v>45453</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44354,7 +44354,7 @@
         <v>44952</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45124</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>45350</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44573,7 +44573,7 @@
         <v>45370</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44646,7 +44646,7 @@
         <v>45373</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44719,7 +44719,7 @@
         <v>44802</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44792,7 +44792,7 @@
         <v>45005</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>44938</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>45194</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>44805</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45084,7 +45084,7 @@
         <v>44896</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45157,7 +45157,7 @@
         <v>45652</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45230,7 +45230,7 @@
         <v>45735</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45737</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>45939</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>45939</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>45980</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>46030</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>46049</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45741,7 +45741,7 @@
         <v>46104</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45814,7 +45814,7 @@
         <v>46134</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45887,7 +45887,7 @@
         <v>46134</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>

--- a/Översikt OSBY.xlsx
+++ b/Översikt OSBY.xlsx
@@ -601,7 +601,7 @@
         <v>45589</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46030</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>46134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45177</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45844</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>44802</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>46318</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>44827</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>46241</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>45796</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>46030</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>46134</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>46134</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>46153</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>46189</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>45356</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>46295</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>45918</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>45867</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>46153</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>45078</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>45607</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>44622</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>44813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>44852</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>44722</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>44788</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>45905</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>45909</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>45364</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45925</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>46170</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>46178</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>46183</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>46189</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>45033</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>45999</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>45649</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>44902</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45799</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45217</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>46275</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>44910</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>45255</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>45126</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>45002</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>44788</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>45177</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>45117</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>44698</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>45272</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         <v>45182</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45446</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>45735</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         <v>44586</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44553</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>44523</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>44579</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>44693</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>44845</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44869</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>44830</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>44603</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>44827</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>44523</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>44522</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>44687</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>44650</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>44813</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>44694</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>44746</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>44572</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>44813</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>44813</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>44529</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>44764</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>44762</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44510</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>44510</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>44575</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>44595</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>44516</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>44505</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>44806</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>44731</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>44610</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>44557</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>44843</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>44609</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>44700</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>44662</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>44830</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>44830</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>44831</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>44823</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>44553</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>44614</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>44788</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>44805</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>44623</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>44788</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>44721</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>44834</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>44610</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>44573</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>44573</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45884</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>45573</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>45483</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>45555</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>44957</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>44631</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>45884</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>45208</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>45016</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>45902</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>45390</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>45239</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>45341</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>45905</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>45436</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>45908</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>45071</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>45342</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>45342</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
         <v>45909</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>46079</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>45911</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>45911</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>45911</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12345,7 +12345,7 @@
         <v>45911</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>45097</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>44711</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>45912</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>45282</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>45632</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12783,7 +12783,7 @@
         <v>45923</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>45321</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>45243</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>45217</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>45079</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>45011</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>45237</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>45371</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>45369</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>45035</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>46170</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>45930</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>45037</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>46170</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>45546</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>44743</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>46175</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45375</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45937</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>45937</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>44904</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>45937</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>45036</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>45937</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>45453</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>44594</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>44783</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>45573</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>45217</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>45385</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>45589</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>45589</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>44823</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>46176</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>45370</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>45119</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45447</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>46076</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45093</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>46176</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44804</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>46180</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>46180</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         <v>44557</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>44557</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>46178</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         <v>46180</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>46183</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>44904</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>45683</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>46183</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>45141</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>45105</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>46183</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45353</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>45443</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45964</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>45268</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>46189</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>46189</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>46189</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>46189</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
         <v>46189</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>46189</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17525,7 +17525,7 @@
         <v>46189</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>46189</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>46189</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>46189</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>46189</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>46189</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45964</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45537</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45971</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>45063</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>45273</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45973</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>46198</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>45628</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>46199</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>45975</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>45648</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>46200</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>46199</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         <v>45033</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>45231</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>45154</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>45453</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>45982</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>44903</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>46205</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>44957</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>45062</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45986</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45208</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45323</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>45362</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>45540</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>45686</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>45520</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>46210</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>45093</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>46213</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45471</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>46213</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>45506</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>46184</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45996</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45404</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>46002</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45777</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45782</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45518</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45702</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>45721</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>44949</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>45474</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>45630</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>46020</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>46020</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>44895</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>45905</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>46029</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>46029</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>46282</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>46282</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>45719</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45448</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>46034</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45019</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>45708</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>46037</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45737</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>45436</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44827</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45356</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>45708</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>45055</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45553</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>45446</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>45471</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>45803</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>46290</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44522</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>45805</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>46289</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23518,7 +23518,7 @@
         <v>46289</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>45635</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         <v>46071</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>46253</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>46076</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45834</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>46254</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>45835</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>46089</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>45838</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>46089</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45838</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>45518</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45826</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>44921</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>46247</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>46100</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>46100</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45845</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45844</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45845</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>46302</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>45434</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>45377</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>46302</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45744</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>45548</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>46303</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>46303</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45453</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>46126</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>46265</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>46265</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>46265</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>46265</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>44610</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>46133</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>46133</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>46133</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26400,7 +26400,7 @@
         <v>46265</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>45162</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>46265</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>44994</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45097</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45362</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>46265</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>44902</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>46265</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27087,7 +27087,7 @@
         <v>45908</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>45785</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27233,7 +27233,7 @@
         <v>45988</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         <v>46310</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27379,7 +27379,7 @@
         <v>46308</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>45666</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>45762</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>45177</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44620</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>46266</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>44620</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>45744</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>44530</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>46267</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45506</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>46266</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>46309</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>44904</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>46267</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>44620</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>46268</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28645,7 +28645,7 @@
         <v>46268</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28718,7 +28718,7 @@
         <v>44881</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>46314</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>45539</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28937,7 +28937,7 @@
         <v>46265</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>45154</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
         <v>45572</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>46268</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>46314</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>46310</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>45575</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>45936</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29531,7 +29531,7 @@
         <v>45369</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>45197</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29677,7 +29677,7 @@
         <v>44935</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>45722</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
         <v>46275</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44965</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>46276</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>44524</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>44524</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>46276</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44904</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>45071</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>44740</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30495,7 +30495,7 @@
         <v>45390</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>45390</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30651,7 +30651,7 @@
         <v>44610</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>45568</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>45364</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
         <v>45588</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45231</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>45961</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>46150</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45524</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>44662</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>45037</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>44679</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>46153</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>46153</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>46153</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>46153</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>45463</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>46153</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>46153</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31995,7 +31995,7 @@
         <v>46155</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32068,7 +32068,7 @@
         <v>45915</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>46155</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>45369</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>45035</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32360,7 +32360,7 @@
         <v>45635</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>44602</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>45607</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32584,7 +32584,7 @@
         <v>45483</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32662,7 +32662,7 @@
         <v>44997</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>45468</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45642</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>44801</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>45642</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45015</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>45091</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>45646</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>44757</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>45605</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>45605</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>45666</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>45630</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>44505</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45646</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45733</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>45688</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>45714</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>45677</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>44832</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45685</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45737</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>44746</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>45685</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>45377</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34517,7 +34517,7 @@
         <v>45730</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>45503</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34663,7 +34663,7 @@
         <v>45255</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34736,7 +34736,7 @@
         <v>45728</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45537</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>45709</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>44994</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>45012</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>45264</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>44838</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>45195</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>45195</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>44965</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>44790</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>45036</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>44910</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45255</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>45259</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>45117</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44900</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>44749</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>45259</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>44902</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>45733</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>44895</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>44826</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>45360</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36498,7 +36498,7 @@
         <v>45723</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>45211</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44872</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>44921</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>45107</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45238</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45240</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>45015</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>45082</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37165,7 +37165,7 @@
         <v>45141</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>45110</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>45002</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37384,7 +37384,7 @@
         <v>45404</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37457,7 +37457,7 @@
         <v>45589</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>45078</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37603,7 +37603,7 @@
         <v>45078</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37676,7 +37676,7 @@
         <v>44557</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>44511</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>44529</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>45096</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37973,7 +37973,7 @@
         <v>45630</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>45063</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>44966</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>44867</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>45141</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>45175</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38411,7 +38411,7 @@
         <v>45656</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>45162</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45643</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38630,7 +38630,7 @@
         <v>45117</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38708,7 +38708,7 @@
         <v>45011</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38781,7 +38781,7 @@
         <v>45471</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>44585</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45534</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45534</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>45217</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39156,7 +39156,7 @@
         <v>45035</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>44832</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>44644</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>45706</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>44658</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>45196</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>44585</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>45119</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>45453</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>45695</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45609</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39964,7 +39964,7 @@
         <v>45148</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>44663</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>45666</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45140</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>45715</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>45686</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>45209</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>44776</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>45194</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>45422</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40694,7 +40694,7 @@
         <v>45631</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>45110</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>45197</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40913,7 +40913,7 @@
         <v>45197</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40986,7 +40986,7 @@
         <v>45301</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41059,7 +41059,7 @@
         <v>45231</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>44790</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41205,7 +41205,7 @@
         <v>45314</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>44802</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>45265</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45237</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41497,7 +41497,7 @@
         <v>45216</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>45555</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>44873</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41716,7 +41716,7 @@
         <v>45733</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>44603</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41867,7 +41867,7 @@
         <v>45147</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>45610</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>44978</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>45652</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>44911</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>45342</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42310,7 +42310,7 @@
         <v>44585</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42383,7 +42383,7 @@
         <v>44580</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>45436</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
         <v>44916</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>44951</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>45414</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>44951</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42821,7 +42821,7 @@
         <v>44742</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>44845</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42967,7 +42967,7 @@
         <v>44656</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>44635</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43113,7 +43113,7 @@
         <v>44719</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43186,7 +43186,7 @@
         <v>44622</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45560</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>44938</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>45476</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43478,7 +43478,7 @@
         <v>44837</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43551,7 +43551,7 @@
         <v>45264</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43624,7 +43624,7 @@
         <v>45400</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43697,7 +43697,7 @@
         <v>45365</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43770,7 +43770,7 @@
         <v>45272</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45622</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44802</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43989,7 +43989,7 @@
         <v>44802</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>44820</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44135,7 +44135,7 @@
         <v>45182</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44208,7 +44208,7 @@
         <v>44806</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44281,7 +44281,7 @@
         <v>45453</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44354,7 +44354,7 @@
         <v>44952</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45124</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>45350</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44573,7 +44573,7 @@
         <v>45370</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44646,7 +44646,7 @@
         <v>45373</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44719,7 +44719,7 @@
         <v>44802</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44792,7 +44792,7 @@
         <v>45005</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>44938</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>45194</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>44805</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45084,7 +45084,7 @@
         <v>44896</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45157,7 +45157,7 @@
         <v>45652</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45230,7 +45230,7 @@
         <v>45735</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45737</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>45939</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>45939</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>45980</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>46030</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>46049</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45741,7 +45741,7 @@
         <v>46104</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45814,7 +45814,7 @@
         <v>46134</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45887,7 +45887,7 @@
         <v>46134</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
